--- a/tagsheet_to_tidbits2025/data/Sander's PIT CODES.xlsx
+++ b/tagsheet_to_tidbits2025/data/Sander's PIT CODES.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://umainesystem-my.sharepoint.com/personal/sander_elliott_maine_edu/Documents/Desktop/Github/Sturgeon_TidBits/tagsheet_to_tidbits2025/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f03cf4e0d6e7cfb9/Desktop/Code/Sturgeon_TidBits/tagsheet_to_tidbits2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{87E30D02-C812-421C-A0AA-2F4032EB8D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0DE24BD-F43B-40F1-BFF1-7D219A7994F7}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{87E30D02-C812-421C-A0AA-2F4032EB8D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C72B015-15B0-438A-B96A-E871B20D540E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trip" sheetId="7" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <sheet name="Trip(1)" sheetId="2" r:id="rId3"/>
-    <sheet name="Trip (2)" sheetId="8" r:id="rId4"/>
-    <sheet name="Trip (3)" sheetId="9" r:id="rId5"/>
-    <sheet name="Trip (4)" sheetId="11" r:id="rId6"/>
-    <sheet name="Trip (5)" sheetId="12" r:id="rId7"/>
+    <sheet name="Sheet1 (2)" sheetId="13" r:id="rId3"/>
+    <sheet name="Trip(1)" sheetId="2" r:id="rId4"/>
+    <sheet name="Trip (2)" sheetId="8" r:id="rId5"/>
+    <sheet name="Trip (3)" sheetId="9" r:id="rId6"/>
+    <sheet name="Trip (4)" sheetId="11" r:id="rId7"/>
+    <sheet name="Trip (5)" sheetId="12" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="214">
   <si>
     <t>3DD.003E185F8C</t>
   </si>
@@ -543,13 +544,151 @@
   </si>
   <si>
     <t>NO RIGHT PEC</t>
+  </si>
+  <si>
+    <t>1645258</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>MAINE DEPT OF MARINE RESOURCES</t>
+  </si>
+  <si>
+    <t>Joseph Zydlewski</t>
+  </si>
+  <si>
+    <t>V16-4x-BLU-1</t>
+  </si>
+  <si>
+    <t>1645259</t>
+  </si>
+  <si>
+    <t>1645260</t>
+  </si>
+  <si>
+    <t>1645261</t>
+  </si>
+  <si>
+    <t>1645262</t>
+  </si>
+  <si>
+    <t>1645263</t>
+  </si>
+  <si>
+    <t>1645264</t>
+  </si>
+  <si>
+    <t>1645265</t>
+  </si>
+  <si>
+    <t>1645266</t>
+  </si>
+  <si>
+    <t>1645267</t>
+  </si>
+  <si>
+    <t>1645268</t>
+  </si>
+  <si>
+    <t>1645269</t>
+  </si>
+  <si>
+    <t>1645270</t>
+  </si>
+  <si>
+    <t>1645271</t>
+  </si>
+  <si>
+    <t>1645272</t>
+  </si>
+  <si>
+    <t>1645273</t>
+  </si>
+  <si>
+    <t>1645274</t>
+  </si>
+  <si>
+    <t>1645275</t>
+  </si>
+  <si>
+    <t>1645276</t>
+  </si>
+  <si>
+    <t>1645277</t>
+  </si>
+  <si>
+    <t>1645278</t>
+  </si>
+  <si>
+    <t>1645279</t>
+  </si>
+  <si>
+    <t>1645280</t>
+  </si>
+  <si>
+    <t>1645281</t>
+  </si>
+  <si>
+    <t>1645282</t>
+  </si>
+  <si>
+    <t>1645283</t>
+  </si>
+  <si>
+    <t>1645284</t>
+  </si>
+  <si>
+    <t>1645285</t>
+  </si>
+  <si>
+    <t>1645286</t>
+  </si>
+  <si>
+    <t>1645287</t>
+  </si>
+  <si>
+    <t>1645288</t>
+  </si>
+  <si>
+    <t>1645289</t>
+  </si>
+  <si>
+    <t>1645290</t>
+  </si>
+  <si>
+    <t>1645291</t>
+  </si>
+  <si>
+    <t>1645292</t>
+  </si>
+  <si>
+    <t>1645293</t>
+  </si>
+  <si>
+    <t>1645294</t>
+  </si>
+  <si>
+    <t>1645295</t>
+  </si>
+  <si>
+    <t>1645296</t>
+  </si>
+  <si>
+    <t>1645297</t>
+  </si>
+  <si>
+    <t>1645298</t>
+  </si>
+  <si>
+    <t>1645299</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -689,6 +828,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1078,7 +1222,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1121,8 +1265,9 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
@@ -1150,8 +1295,10 @@
     <xf numFmtId="0" fontId="17" fillId="13" borderId="11" xfId="22" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1189,13 +1336,24 @@
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="42" xr:uid="{8D2619A1-7999-4244-81BC-02B86FBC88EF}"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1601,29 +1759,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9EDA711-86F6-489C-9871-79414856E4C9}">
   <dimension ref="A1:Y38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" customWidth="1"/>
-    <col min="17" max="17" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.54296875" customWidth="1"/>
+    <col min="10" max="10" width="7.7265625" customWidth="1"/>
+    <col min="11" max="11" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7265625" customWidth="1"/>
+    <col min="17" max="17" width="12.1796875" customWidth="1"/>
     <col min="18" max="18" width="4" customWidth="1"/>
-    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>88</v>
       </c>
@@ -1694,7 +1852,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
       <c r="H2" s="5"/>
@@ -1721,7 +1879,7 @@
       </c>
       <c r="T2" s="1"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F3" s="2"/>
       <c r="H3" s="8"/>
       <c r="I3" s="2"/>
@@ -1739,7 +1897,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F4" s="2"/>
       <c r="H4" s="8"/>
       <c r="I4" s="2"/>
@@ -1757,7 +1915,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F5" s="2"/>
       <c r="H5" s="8"/>
       <c r="I5" s="2"/>
@@ -1775,7 +1933,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F6" s="2"/>
       <c r="H6" s="8"/>
       <c r="I6" s="2"/>
@@ -1793,7 +1951,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F7" s="2"/>
       <c r="H7" s="8"/>
       <c r="I7" s="2"/>
@@ -1811,7 +1969,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F8" s="2"/>
       <c r="H8" s="9"/>
       <c r="I8" s="2"/>
@@ -1829,7 +1987,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -1847,7 +2005,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -1865,7 +2023,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -1883,7 +2041,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1897,7 +2055,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -1911,7 +2069,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -1925,7 +2083,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -1939,7 +2097,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -1953,7 +2111,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -1967,7 +2125,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -1981,7 +2139,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -1995,7 +2153,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -2009,7 +2167,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -2023,7 +2181,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -2037,7 +2195,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -2051,7 +2209,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -2065,7 +2223,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -2079,7 +2237,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -2093,7 +2251,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -2107,7 +2265,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -2121,7 +2279,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -2135,7 +2293,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -2149,7 +2307,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -2163,7 +2321,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -2177,7 +2335,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -2191,7 +2349,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -2205,7 +2363,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -2215,7 +2373,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -2225,25 +2383,25 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F38" s="2"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <conditionalFormatting sqref="Q2:Q100">
-    <cfRule type="expression" dxfId="12" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="1" stopIfTrue="1">
       <formula>AND($Q2&lt;&gt;$B2, $Q2&lt;&gt;"UKN", $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="2">
+    <cfRule type="expression" dxfId="12" priority="2">
       <formula>$Q2="UKN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="3" stopIfTrue="1">
       <formula>AND($Q2=$B2, $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2254,13 +2412,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>61</v>
       </c>
@@ -2277,7 +2435,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2295,7 +2453,7 @@
         <v>201133</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2313,7 +2471,7 @@
         <v>201127</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2331,7 +2489,7 @@
         <v>201134</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2349,7 +2507,7 @@
         <v>201128</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2367,7 +2525,7 @@
         <v>201129</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2385,7 +2543,7 @@
         <v>201131</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2403,7 +2561,7 @@
         <v>201130</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2421,7 +2579,7 @@
         <v>201132</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2439,7 +2597,7 @@
         <v>201212</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2457,7 +2615,7 @@
         <v>201215</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2475,7 +2633,7 @@
         <v>201213</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2493,7 +2651,7 @@
         <v>201214</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2511,7 +2669,7 @@
         <v>201216</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2529,7 +2687,7 @@
         <v>201217</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2547,7 +2705,7 @@
         <v>201218</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2565,7 +2723,7 @@
         <v>201219</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2583,7 +2741,7 @@
         <v>201220</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2601,7 +2759,7 @@
         <v>201223</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2619,7 +2777,7 @@
         <v>201222</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2637,7 +2795,7 @@
         <v>201221</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2655,7 +2813,7 @@
         <v>201224</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2673,7 +2831,7 @@
         <v>201225</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2691,7 +2849,7 @@
         <v>201226</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2709,7 +2867,7 @@
         <v>201227</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2727,7 +2885,7 @@
         <v>201228</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2745,7 +2903,7 @@
         <v>201229</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2763,7 +2921,7 @@
         <v>201232</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2781,7 +2939,7 @@
         <v>201231</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2799,7 +2957,7 @@
         <v>201230</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2817,7 +2975,7 @@
         <v>201235</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2835,7 +2993,7 @@
         <v>201234</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2853,7 +3011,7 @@
         <v>201233</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2871,7 +3029,7 @@
         <v>201238</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2889,7 +3047,7 @@
         <v>201237</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2907,7 +3065,7 @@
         <v>201236</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2925,7 +3083,7 @@
         <v>201239</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2943,7 +3101,7 @@
         <v>201240</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2961,7 +3119,7 @@
         <v>201241</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2979,7 +3137,7 @@
         <v>201244</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2997,7 +3155,7 @@
         <v>201243</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3015,7 +3173,7 @@
         <v>201242</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3033,7 +3191,7 @@
         <v>201247</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3051,7 +3209,7 @@
         <v>201246</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3069,7 +3227,7 @@
         <v>201245</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3087,7 +3245,7 @@
         <v>201252</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3105,7 +3263,7 @@
         <v>201249</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3123,7 +3281,7 @@
         <v>201253</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3141,7 +3299,7 @@
         <v>201250</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3159,7 +3317,7 @@
         <v>201248</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3177,7 +3335,7 @@
         <v>201251</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3185,7 +3343,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3193,7 +3351,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3201,7 +3359,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3209,7 +3367,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3217,7 +3375,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3225,7 +3383,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3233,7 +3391,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3241,7 +3399,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3249,7 +3407,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3261,7 +3419,7 @@
   <sheetProtection algorithmName="SHA-512" hashValue="GLBxjVtZqvzkQTPGUZuo+WHi4zuX2+iRK7ponll4YJu7jFzCXRgL29u+SxlJRXoxg9VxoqC0XidWHTkVsfdCng==" saltValue="otX8nHZYZ6RQ5YCUGUc8Og==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="F2:F51">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3269,31 +3427,1802 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0019F054-F7CA-421F-8EA8-E60A6BBFF39A}">
+  <dimension ref="A1:M61"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2">
+        <f>VALUE(RIGHT(E2,6))</f>
+        <v>201133</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F51" si="0">VALUE(RIGHT(E3,6))</f>
+        <v>201127</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>201134</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>201128</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>201129</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>201131</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>201130</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>201132</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>201212</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>201215</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>201213</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>201214</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>201216</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>201217</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>201218</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>201219</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>201220</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>201223</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20">
+        <v>19</v>
+      </c>
+      <c r="E20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>201222</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+      <c r="E21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>201221</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22">
+        <v>21</v>
+      </c>
+      <c r="E22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>201224</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M22" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23">
+        <v>22</v>
+      </c>
+      <c r="E23" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>201225</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>201226</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25">
+        <v>24</v>
+      </c>
+      <c r="E25" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>201227</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>201228</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>201229</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L27" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M27" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28">
+        <v>27</v>
+      </c>
+      <c r="E28" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>201232</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>102</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>201231</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30">
+        <v>29</v>
+      </c>
+      <c r="E30" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>201230</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31">
+        <v>30</v>
+      </c>
+      <c r="E31" t="s">
+        <v>104</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>201235</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L31" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M31" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32">
+        <v>31</v>
+      </c>
+      <c r="E32" t="s">
+        <v>105</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>201234</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L32" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M32" s="15" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33">
+        <v>32</v>
+      </c>
+      <c r="E33" t="s">
+        <v>106</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>201233</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L33" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34">
+        <v>33</v>
+      </c>
+      <c r="E34" t="s">
+        <v>107</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>201238</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L34" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M34" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35">
+        <v>34</v>
+      </c>
+      <c r="E35" t="s">
+        <v>108</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>201237</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="I35" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J35" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L35" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36">
+        <v>35</v>
+      </c>
+      <c r="E36" t="s">
+        <v>109</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>201236</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L36" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M36" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37">
+        <v>36</v>
+      </c>
+      <c r="E37" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>201239</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L37" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38">
+        <v>37</v>
+      </c>
+      <c r="E38" t="s">
+        <v>111</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>201240</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K38" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L38" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M38" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39">
+        <v>38</v>
+      </c>
+      <c r="E39" t="s">
+        <v>112</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>201241</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J39" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K39" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L39" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M39" s="15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40">
+        <v>39</v>
+      </c>
+      <c r="E40" t="s">
+        <v>113</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>201244</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J40" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L40" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M40" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41">
+        <v>40</v>
+      </c>
+      <c r="E41" t="s">
+        <v>114</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>201243</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J41" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L41" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M41" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42">
+        <v>41</v>
+      </c>
+      <c r="E42" t="s">
+        <v>115</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="0"/>
+        <v>201242</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M42" s="15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43">
+        <v>42</v>
+      </c>
+      <c r="E43" t="s">
+        <v>116</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="0"/>
+        <v>201247</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="I43" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J43" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="M43" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44">
+        <v>43</v>
+      </c>
+      <c r="E44" t="s">
+        <v>117</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="0"/>
+        <v>201246</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>43</v>
+      </c>
+      <c r="D45">
+        <v>44</v>
+      </c>
+      <c r="E45" t="s">
+        <v>118</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="0"/>
+        <v>201245</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46">
+        <v>45</v>
+      </c>
+      <c r="E46" t="s">
+        <v>162</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="0"/>
+        <v>201252</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47">
+        <v>46</v>
+      </c>
+      <c r="E47" t="s">
+        <v>157</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="0"/>
+        <v>201249</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>46</v>
+      </c>
+      <c r="D48">
+        <v>47</v>
+      </c>
+      <c r="E48" t="s">
+        <v>158</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="0"/>
+        <v>201253</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49">
+        <v>48</v>
+      </c>
+      <c r="E49" t="s">
+        <v>159</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="0"/>
+        <v>201250</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50">
+        <v>49</v>
+      </c>
+      <c r="E50" t="s">
+        <v>160</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="0"/>
+        <v>201248</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>49</v>
+      </c>
+      <c r="D51">
+        <v>50</v>
+      </c>
+      <c r="E51" t="s">
+        <v>161</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="0"/>
+        <v>201251</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F2:F51">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FD9965-3A02-44AF-9BF4-86BFA009B4F7}">
   <dimension ref="A1:Y38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.54296875" customWidth="1"/>
+    <col min="10" max="10" width="7.7265625" customWidth="1"/>
+    <col min="11" max="11" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.140625" customWidth="1"/>
+    <col min="17" max="17" width="12.1796875" customWidth="1"/>
     <col min="18" max="18" width="4" customWidth="1"/>
-    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>88</v>
       </c>
@@ -3364,7 +5293,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3433,7 +5362,7 @@
         <v>4899033</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3487,7 +5416,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3541,7 +5470,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3593,7 +5522,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3647,7 +5576,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3704,7 +5633,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3758,7 +5687,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3812,7 +5741,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3869,7 +5798,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3926,1261 +5855,163 @@
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F38" s="2"/>
-    </row>
-  </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83D4C17-C0AD-48BE-80DF-6BA497415298}">
-  <dimension ref="A1:Y38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6" customWidth="1"/>
-    <col min="17" max="17" width="12.140625" customWidth="1"/>
-    <col min="18" max="18" width="4" customWidth="1"/>
-    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="T1" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="U1" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="V1" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="W1" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="X1" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y1" s="14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2">
-        <v>11</v>
-      </c>
-      <c r="D2">
-        <v>201219</v>
-      </c>
-      <c r="E2">
-        <v>11</v>
-      </c>
-      <c r="F2" s="5">
-        <v>73.099999999999994</v>
-      </c>
-      <c r="G2" s="6">
-        <v>88.2</v>
-      </c>
-      <c r="H2" s="5">
-        <v>54</v>
-      </c>
-      <c r="I2" s="5">
-        <v>36</v>
-      </c>
-      <c r="J2" s="7">
-        <v>41</v>
-      </c>
-      <c r="K2" t="s">
-        <v>132</v>
-      </c>
-      <c r="N2" t="str">
-        <f>_xlfn.XLOOKUP(C2, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F7F</v>
-      </c>
-      <c r="O2" t="str">
-        <f>IF(D2="", "", _xlfn.XLOOKUP(D2, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201219</v>
-      </c>
-      <c r="P2">
-        <f>IF(OR(I2="",H2=""),"",I2/H2)</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="Q2" t="str">
-        <f>IF(P2="", "UKN", IF(P2&lt;0.55, "AST", IF(P2&gt;0.62, "SNS", "UKN")))</f>
-        <v>SNS</v>
-      </c>
-      <c r="R2" t="s">
-        <v>136</v>
-      </c>
-      <c r="T2" s="1">
-        <v>45873</v>
-      </c>
-      <c r="U2" t="s">
-        <v>124</v>
-      </c>
-      <c r="V2" t="s">
-        <v>139</v>
-      </c>
-      <c r="W2">
-        <v>437291</v>
-      </c>
-      <c r="X2">
-        <v>4902372</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C3">
-        <v>12</v>
-      </c>
-      <c r="D3">
-        <v>201218</v>
-      </c>
-      <c r="E3">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2">
-        <v>68.900000000000006</v>
-      </c>
-      <c r="G3">
-        <v>82.8</v>
-      </c>
-      <c r="H3" s="8">
-        <v>57</v>
-      </c>
-      <c r="I3" s="2">
-        <v>38</v>
-      </c>
-      <c r="J3" s="3">
-        <v>46</v>
-      </c>
-      <c r="K3" t="s">
-        <v>132</v>
-      </c>
-      <c r="N3" t="str">
-        <f>_xlfn.XLOOKUP(C3, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F94</v>
-      </c>
-      <c r="O3" t="str">
-        <f>IF(D3="", "", _xlfn.XLOOKUP(D3, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201218</v>
-      </c>
-      <c r="P3">
-        <f t="shared" ref="P3:P15" si="0">IF(OR(I3="",H3=""),"",I3/H3)</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q15" si="1">IF(P3="", "UKN", IF(P3&lt;0.55, "AST", IF(P3&gt;0.62, "SNS", "UKN")))</f>
-        <v>SNS</v>
-      </c>
-      <c r="R3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4">
-        <v>13</v>
-      </c>
-      <c r="D4">
-        <v>201216</v>
-      </c>
-      <c r="E4">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2">
-        <v>65.599999999999994</v>
-      </c>
-      <c r="G4">
-        <v>76.599999999999994</v>
-      </c>
-      <c r="H4" s="8">
-        <v>51</v>
-      </c>
-      <c r="I4" s="2">
-        <v>40</v>
-      </c>
-      <c r="J4" s="3">
-        <v>47</v>
-      </c>
-      <c r="K4" t="s">
-        <v>132</v>
-      </c>
-      <c r="N4" t="str">
-        <f>_xlfn.XLOOKUP(C4, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F74</v>
-      </c>
-      <c r="O4" t="str">
-        <f>IF(D4="", "", _xlfn.XLOOKUP(D4, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201216</v>
-      </c>
-      <c r="P4">
-        <f t="shared" si="0"/>
-        <v>0.78431372549019607</v>
-      </c>
-      <c r="Q4" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5">
-        <v>14</v>
-      </c>
-      <c r="D5">
-        <v>201221</v>
-      </c>
-      <c r="E5">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2">
-        <v>75.8</v>
-      </c>
-      <c r="G5">
-        <v>86.2</v>
-      </c>
-      <c r="H5" s="8">
-        <v>59</v>
-      </c>
-      <c r="I5" s="2">
-        <v>46</v>
-      </c>
-      <c r="J5" s="3">
-        <v>54</v>
-      </c>
-      <c r="K5" t="s">
-        <v>132</v>
-      </c>
-      <c r="L5" t="s">
-        <v>167</v>
-      </c>
-      <c r="N5" t="str">
-        <f>_xlfn.XLOOKUP(C5, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F91</v>
-      </c>
-      <c r="O5" t="str">
-        <f>IF(D5="", "", _xlfn.XLOOKUP(D5, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201221</v>
-      </c>
-      <c r="P5">
-        <f t="shared" si="0"/>
-        <v>0.77966101694915257</v>
-      </c>
-      <c r="Q5" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-      <c r="D6">
-        <v>201220</v>
-      </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
-      <c r="F6" s="2">
-        <v>65.2</v>
-      </c>
-      <c r="G6">
-        <v>77.099999999999994</v>
-      </c>
-      <c r="H6" s="8">
-        <v>50</v>
-      </c>
-      <c r="I6" s="2">
-        <v>36</v>
-      </c>
-      <c r="J6" s="3">
-        <v>43</v>
-      </c>
-      <c r="K6" t="s">
-        <v>132</v>
-      </c>
-      <c r="L6" t="s">
-        <v>142</v>
-      </c>
-      <c r="N6" t="str">
-        <f>_xlfn.XLOOKUP(C6, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F90</v>
-      </c>
-      <c r="O6" t="str">
-        <f>IF(D6="", "", _xlfn.XLOOKUP(D6, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201220</v>
-      </c>
-      <c r="P6">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
-      </c>
-      <c r="Q6" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7">
-        <v>16</v>
-      </c>
-      <c r="D7">
-        <v>201129</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7" s="2">
-        <v>74</v>
-      </c>
-      <c r="G7">
-        <v>84.8</v>
-      </c>
-      <c r="H7" s="8">
-        <v>57</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44</v>
-      </c>
-      <c r="J7" s="3">
-        <v>55</v>
-      </c>
-      <c r="K7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L7" t="s">
-        <v>143</v>
-      </c>
-      <c r="N7" t="str">
-        <f>_xlfn.XLOOKUP(C7, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F78</v>
-      </c>
-      <c r="O7" t="str">
-        <f>IF(D7="", "", _xlfn.XLOOKUP(D7, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201129</v>
-      </c>
-      <c r="P7">
-        <f t="shared" si="0"/>
-        <v>0.77192982456140347</v>
-      </c>
-      <c r="Q7" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8">
-        <v>17</v>
-      </c>
-      <c r="D8">
-        <v>201223</v>
-      </c>
-      <c r="E8">
-        <v>17</v>
-      </c>
-      <c r="F8" s="2">
-        <v>65.8</v>
-      </c>
-      <c r="G8">
-        <v>76.8</v>
-      </c>
-      <c r="H8" s="9">
-        <v>49</v>
-      </c>
-      <c r="I8" s="2">
-        <v>37</v>
-      </c>
-      <c r="J8" s="3">
-        <v>46</v>
-      </c>
-      <c r="K8" t="s">
-        <v>132</v>
-      </c>
-      <c r="N8" t="str">
-        <f>_xlfn.XLOOKUP(C8, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F87</v>
-      </c>
-      <c r="O8" t="str">
-        <f>IF(D8="", "", _xlfn.XLOOKUP(D8, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201223</v>
-      </c>
-      <c r="P8">
-        <f t="shared" si="0"/>
-        <v>0.75510204081632648</v>
-      </c>
-      <c r="Q8" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9">
-        <v>18</v>
-      </c>
-      <c r="D9">
-        <v>201222</v>
-      </c>
-      <c r="E9">
-        <v>18</v>
-      </c>
-      <c r="F9" s="2">
-        <v>70.599999999999994</v>
-      </c>
-      <c r="G9">
-        <v>82.6</v>
-      </c>
-      <c r="H9" s="2">
-        <v>52</v>
-      </c>
-      <c r="I9" s="2">
-        <v>44</v>
-      </c>
-      <c r="J9" s="3">
-        <v>51</v>
-      </c>
-      <c r="K9" t="s">
-        <v>132</v>
-      </c>
-      <c r="N9" t="str">
-        <f>_xlfn.XLOOKUP(C9, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F6C</v>
-      </c>
-      <c r="O9" t="str">
-        <f>IF(D9="", "", _xlfn.XLOOKUP(D9, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201222</v>
-      </c>
-      <c r="P9">
-        <f t="shared" si="0"/>
-        <v>0.84615384615384615</v>
-      </c>
-      <c r="Q9" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>140</v>
-      </c>
-      <c r="C10">
-        <v>19</v>
-      </c>
-      <c r="D10">
-        <v>201217</v>
-      </c>
-      <c r="E10">
-        <v>19</v>
-      </c>
-      <c r="F10" s="2">
-        <v>68.2</v>
-      </c>
-      <c r="G10">
-        <v>82.6</v>
-      </c>
-      <c r="H10" s="2">
-        <v>51</v>
-      </c>
-      <c r="I10" s="2">
-        <v>44</v>
-      </c>
-      <c r="J10" s="3">
-        <v>52</v>
-      </c>
-      <c r="K10" t="s">
-        <v>132</v>
-      </c>
-      <c r="N10" t="str">
-        <f>_xlfn.XLOOKUP(C10, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F89</v>
-      </c>
-      <c r="O10" t="str">
-        <f>IF(D10="", "", _xlfn.XLOOKUP(D10, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201217</v>
-      </c>
-      <c r="P10">
-        <f t="shared" si="0"/>
-        <v>0.86274509803921573</v>
-      </c>
-      <c r="Q10" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C11">
-        <v>20</v>
-      </c>
-      <c r="D11">
-        <v>201214</v>
-      </c>
-      <c r="E11">
-        <v>20</v>
-      </c>
-      <c r="F11" s="2">
-        <v>58.8</v>
-      </c>
-      <c r="G11">
-        <v>70.400000000000006</v>
-      </c>
-      <c r="H11" s="2">
-        <v>51</v>
-      </c>
-      <c r="I11" s="2">
-        <v>35</v>
-      </c>
-      <c r="J11" s="3">
-        <v>43</v>
-      </c>
-      <c r="K11" t="s">
-        <v>132</v>
-      </c>
-      <c r="N11" t="str">
-        <f>_xlfn.XLOOKUP(C11, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F8E</v>
-      </c>
-      <c r="O11" t="str">
-        <f>IF(D11="", "", _xlfn.XLOOKUP(D11, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201214</v>
-      </c>
-      <c r="P11">
-        <f t="shared" si="0"/>
-        <v>0.68627450980392157</v>
-      </c>
-      <c r="Q11" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12">
-        <v>21</v>
-      </c>
-      <c r="D12">
-        <v>201213</v>
-      </c>
-      <c r="E12">
-        <v>21</v>
-      </c>
-      <c r="F12" s="2">
-        <v>59</v>
-      </c>
-      <c r="G12">
-        <v>69.599999999999994</v>
-      </c>
-      <c r="H12" s="2">
-        <v>47</v>
-      </c>
-      <c r="I12" s="2">
-        <v>36</v>
-      </c>
-      <c r="J12" s="3">
-        <v>42</v>
-      </c>
-      <c r="K12" t="s">
-        <v>132</v>
-      </c>
-      <c r="N12" t="str">
-        <f>_xlfn.XLOOKUP(C12, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F88</v>
-      </c>
-      <c r="O12" t="str">
-        <f>IF(D12="", "", _xlfn.XLOOKUP(D12, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201213</v>
-      </c>
-      <c r="P12">
-        <f t="shared" si="0"/>
-        <v>0.76595744680851063</v>
-      </c>
-      <c r="Q12" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C13">
-        <v>23</v>
-      </c>
-      <c r="D13">
-        <v>201225</v>
-      </c>
-      <c r="E13">
-        <v>22</v>
-      </c>
-      <c r="F13" s="2">
-        <v>63.4</v>
-      </c>
-      <c r="G13">
-        <v>75.2</v>
-      </c>
-      <c r="H13" s="2">
-        <v>46</v>
-      </c>
-      <c r="I13" s="2">
-        <v>35</v>
-      </c>
-      <c r="J13" s="3">
-        <v>43</v>
-      </c>
-      <c r="K13" t="s">
-        <v>132</v>
-      </c>
-      <c r="N13" t="str">
-        <f>_xlfn.XLOOKUP(C13, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F85</v>
-      </c>
-      <c r="O13" t="str">
-        <f>IF(D13="", "", _xlfn.XLOOKUP(D13, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201225</v>
-      </c>
-      <c r="P13">
-        <f t="shared" si="0"/>
-        <v>0.76086956521739135</v>
-      </c>
-      <c r="Q13" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R13" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14">
-        <v>24</v>
-      </c>
-      <c r="D14">
-        <v>201224</v>
-      </c>
-      <c r="E14">
-        <v>23</v>
-      </c>
-      <c r="F14" s="2">
-        <v>65.400000000000006</v>
-      </c>
-      <c r="G14">
-        <v>77</v>
-      </c>
-      <c r="H14" s="2">
-        <v>51</v>
-      </c>
-      <c r="I14" s="2">
-        <v>57</v>
-      </c>
-      <c r="J14" s="3">
-        <v>45</v>
-      </c>
-      <c r="K14" t="s">
-        <v>132</v>
-      </c>
-      <c r="N14" t="str">
-        <f>_xlfn.XLOOKUP(C14, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F68</v>
-      </c>
-      <c r="O14" t="str">
-        <f>IF(D14="", "", _xlfn.XLOOKUP(D14, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201224</v>
-      </c>
-      <c r="P14">
-        <f t="shared" si="0"/>
-        <v>1.1176470588235294</v>
-      </c>
-      <c r="Q14" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s">
-        <v>140</v>
-      </c>
-      <c r="C15">
-        <v>25</v>
-      </c>
-      <c r="E15">
-        <v>24</v>
-      </c>
-      <c r="F15" s="2">
-        <v>61.4</v>
-      </c>
-      <c r="G15">
-        <v>72.3</v>
-      </c>
-      <c r="H15" s="2">
-        <v>47</v>
-      </c>
-      <c r="I15" s="2">
-        <v>36</v>
-      </c>
-      <c r="J15" s="3">
-        <v>43</v>
-      </c>
-      <c r="K15" t="s">
-        <v>132</v>
-      </c>
-      <c r="N15" t="str">
-        <f>_xlfn.XLOOKUP(C15, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F69</v>
-      </c>
-      <c r="O15" t="str">
-        <f>IF(D15="", "", _xlfn.XLOOKUP(D15, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-      <c r="P15">
-        <f t="shared" si="0"/>
-        <v>0.76595744680851063</v>
-      </c>
-      <c r="Q15" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="F16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="3"/>
-      <c r="O16" t="str">
-        <f>IF(D16="", "", _xlfn.XLOOKUP(D16, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="3"/>
-      <c r="O17" t="str">
-        <f>IF(D17="", "", _xlfn.XLOOKUP(D17, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="3"/>
-      <c r="O18" t="str">
-        <f>IF(D18="", "", _xlfn.XLOOKUP(D18, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="3"/>
-      <c r="O19" t="str">
-        <f>IF(D19="", "", _xlfn.XLOOKUP(D19, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="3"/>
-      <c r="O20" t="str">
-        <f>IF(D20="", "", _xlfn.XLOOKUP(D20, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="3"/>
-      <c r="O21" t="str">
-        <f>IF(D21="", "", _xlfn.XLOOKUP(D21, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="3"/>
-      <c r="O22" t="str">
-        <f>IF(D22="", "", _xlfn.XLOOKUP(D22, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="3"/>
-      <c r="O23" t="str">
-        <f>IF(D23="", "", _xlfn.XLOOKUP(D23, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="3"/>
-      <c r="O24" t="str">
-        <f>IF(D24="", "", _xlfn.XLOOKUP(D24, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="3"/>
-      <c r="O25" t="str">
-        <f>IF(D25="", "", _xlfn.XLOOKUP(D25, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="3"/>
-      <c r="O26" t="str">
-        <f>IF(D26="", "", _xlfn.XLOOKUP(D26, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="3"/>
-      <c r="O27" t="str">
-        <f>IF(D27="", "", _xlfn.XLOOKUP(D27, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="3"/>
-      <c r="O28" t="str">
-        <f>IF(D28="", "", _xlfn.XLOOKUP(D28, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="3"/>
-      <c r="O29" t="str">
-        <f>IF(D29="", "", _xlfn.XLOOKUP(D29, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="3"/>
-      <c r="O30" t="str">
-        <f>IF(D30="", "", _xlfn.XLOOKUP(D30, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="3"/>
-      <c r="O31" t="str">
-        <f>IF(D31="", "", _xlfn.XLOOKUP(D31, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="3"/>
-      <c r="O32" t="str">
-        <f>IF(D32="", "", _xlfn.XLOOKUP(D32, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="3"/>
-      <c r="O33" t="str">
-        <f>IF(D33="", "", _xlfn.XLOOKUP(D33, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="3"/>
-      <c r="O34" t="str">
-        <f>IF(D34="", "", _xlfn.XLOOKUP(D34, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="3"/>
-      <c r="O35" t="str">
-        <f>IF(D35="", "", _xlfn.XLOOKUP(D35, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="3"/>
-      <c r="O36" t="str">
-        <f>IF(D36="", "", _xlfn.XLOOKUP(D36, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="6:15" x14ac:dyDescent="0.25">
-      <c r="F37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="3"/>
-    </row>
-    <row r="38" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F38" s="2"/>
     </row>
   </sheetData>
@@ -5190,31 +6021,1129 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83D4C17-C0AD-48BE-80DF-6BA497415298}">
+  <dimension ref="A1:Y38"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.54296875" customWidth="1"/>
+    <col min="10" max="10" width="7.7265625" customWidth="1"/>
+    <col min="11" max="11" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6" customWidth="1"/>
+    <col min="17" max="17" width="12.1796875" customWidth="1"/>
+    <col min="18" max="18" width="4" customWidth="1"/>
+    <col min="20" max="20" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="T1" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="U1" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="V1" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="W1" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="X1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y1" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2">
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <v>201219</v>
+      </c>
+      <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2" s="5">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="G2" s="6">
+        <v>88.2</v>
+      </c>
+      <c r="H2" s="5">
+        <v>54</v>
+      </c>
+      <c r="I2" s="5">
+        <v>36</v>
+      </c>
+      <c r="J2" s="7">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N2" t="str">
+        <f>_xlfn.XLOOKUP(C2, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F7F</v>
+      </c>
+      <c r="O2" t="str">
+        <f>IF(D2="", "", _xlfn.XLOOKUP(D2, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201219</v>
+      </c>
+      <c r="P2">
+        <f>IF(OR(I2="",H2=""),"",I2/H2)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Q2" t="str">
+        <f>IF(P2="", "UKN", IF(P2&lt;0.55, "AST", IF(P2&gt;0.62, "SNS", "UKN")))</f>
+        <v>SNS</v>
+      </c>
+      <c r="R2" t="s">
+        <v>136</v>
+      </c>
+      <c r="T2" s="1">
+        <v>45873</v>
+      </c>
+      <c r="U2" t="s">
+        <v>124</v>
+      </c>
+      <c r="V2" t="s">
+        <v>139</v>
+      </c>
+      <c r="W2">
+        <v>437291</v>
+      </c>
+      <c r="X2">
+        <v>4902372</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>201218</v>
+      </c>
+      <c r="E3">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="G3">
+        <v>82.8</v>
+      </c>
+      <c r="H3" s="8">
+        <v>57</v>
+      </c>
+      <c r="I3" s="2">
+        <v>38</v>
+      </c>
+      <c r="J3" s="3">
+        <v>46</v>
+      </c>
+      <c r="K3" t="s">
+        <v>132</v>
+      </c>
+      <c r="N3" t="str">
+        <f>_xlfn.XLOOKUP(C3, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F94</v>
+      </c>
+      <c r="O3" t="str">
+        <f>IF(D3="", "", _xlfn.XLOOKUP(D3, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201218</v>
+      </c>
+      <c r="P3">
+        <f t="shared" ref="P3:P15" si="0">IF(OR(I3="",H3=""),"",I3/H3)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Q3" t="str">
+        <f t="shared" ref="Q3:Q15" si="1">IF(P3="", "UKN", IF(P3&lt;0.55, "AST", IF(P3&gt;0.62, "SNS", "UKN")))</f>
+        <v>SNS</v>
+      </c>
+      <c r="R3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4">
+        <v>13</v>
+      </c>
+      <c r="D4">
+        <v>201216</v>
+      </c>
+      <c r="E4">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="G4">
+        <v>76.599999999999994</v>
+      </c>
+      <c r="H4" s="8">
+        <v>51</v>
+      </c>
+      <c r="I4" s="2">
+        <v>40</v>
+      </c>
+      <c r="J4" s="3">
+        <v>47</v>
+      </c>
+      <c r="K4" t="s">
+        <v>132</v>
+      </c>
+      <c r="N4" t="str">
+        <f>_xlfn.XLOOKUP(C4, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F74</v>
+      </c>
+      <c r="O4" t="str">
+        <f>IF(D4="", "", _xlfn.XLOOKUP(D4, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201216</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="0"/>
+        <v>0.78431372549019607</v>
+      </c>
+      <c r="Q4" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>201221</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2">
+        <v>75.8</v>
+      </c>
+      <c r="G5">
+        <v>86.2</v>
+      </c>
+      <c r="H5" s="8">
+        <v>59</v>
+      </c>
+      <c r="I5" s="2">
+        <v>46</v>
+      </c>
+      <c r="J5" s="3">
+        <v>54</v>
+      </c>
+      <c r="K5" t="s">
+        <v>132</v>
+      </c>
+      <c r="L5" t="s">
+        <v>167</v>
+      </c>
+      <c r="N5" t="str">
+        <f>_xlfn.XLOOKUP(C5, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F91</v>
+      </c>
+      <c r="O5" t="str">
+        <f>IF(D5="", "", _xlfn.XLOOKUP(D5, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201221</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="0"/>
+        <v>0.77966101694915257</v>
+      </c>
+      <c r="Q5" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>201220</v>
+      </c>
+      <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2">
+        <v>65.2</v>
+      </c>
+      <c r="G6">
+        <v>77.099999999999994</v>
+      </c>
+      <c r="H6" s="8">
+        <v>50</v>
+      </c>
+      <c r="I6" s="2">
+        <v>36</v>
+      </c>
+      <c r="J6" s="3">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>132</v>
+      </c>
+      <c r="L6" t="s">
+        <v>142</v>
+      </c>
+      <c r="N6" t="str">
+        <f>_xlfn.XLOOKUP(C6, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F90</v>
+      </c>
+      <c r="O6" t="str">
+        <f>IF(D6="", "", _xlfn.XLOOKUP(D6, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201220</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
+      <c r="Q6" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>201129</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2">
+        <v>74</v>
+      </c>
+      <c r="G7">
+        <v>84.8</v>
+      </c>
+      <c r="H7" s="8">
+        <v>57</v>
+      </c>
+      <c r="I7" s="2">
+        <v>44</v>
+      </c>
+      <c r="J7" s="3">
+        <v>55</v>
+      </c>
+      <c r="K7" t="s">
+        <v>132</v>
+      </c>
+      <c r="L7" t="s">
+        <v>143</v>
+      </c>
+      <c r="N7" t="str">
+        <f>_xlfn.XLOOKUP(C7, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F78</v>
+      </c>
+      <c r="O7" t="str">
+        <f>IF(D7="", "", _xlfn.XLOOKUP(D7, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201129</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="0"/>
+        <v>0.77192982456140347</v>
+      </c>
+      <c r="Q7" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>201223</v>
+      </c>
+      <c r="E8">
+        <v>17</v>
+      </c>
+      <c r="F8" s="2">
+        <v>65.8</v>
+      </c>
+      <c r="G8">
+        <v>76.8</v>
+      </c>
+      <c r="H8" s="9">
+        <v>49</v>
+      </c>
+      <c r="I8" s="2">
+        <v>37</v>
+      </c>
+      <c r="J8" s="3">
+        <v>46</v>
+      </c>
+      <c r="K8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N8" t="str">
+        <f>_xlfn.XLOOKUP(C8, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F87</v>
+      </c>
+      <c r="O8" t="str">
+        <f>IF(D8="", "", _xlfn.XLOOKUP(D8, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201223</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>0.75510204081632648</v>
+      </c>
+      <c r="Q8" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9">
+        <v>18</v>
+      </c>
+      <c r="D9">
+        <v>201222</v>
+      </c>
+      <c r="E9">
+        <v>18</v>
+      </c>
+      <c r="F9" s="2">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="G9">
+        <v>82.6</v>
+      </c>
+      <c r="H9" s="2">
+        <v>52</v>
+      </c>
+      <c r="I9" s="2">
+        <v>44</v>
+      </c>
+      <c r="J9" s="3">
+        <v>51</v>
+      </c>
+      <c r="K9" t="s">
+        <v>132</v>
+      </c>
+      <c r="N9" t="str">
+        <f>_xlfn.XLOOKUP(C9, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F6C</v>
+      </c>
+      <c r="O9" t="str">
+        <f>IF(D9="", "", _xlfn.XLOOKUP(D9, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201222</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="0"/>
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Q9" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10">
+        <v>19</v>
+      </c>
+      <c r="D10">
+        <v>201217</v>
+      </c>
+      <c r="E10">
+        <v>19</v>
+      </c>
+      <c r="F10" s="2">
+        <v>68.2</v>
+      </c>
+      <c r="G10">
+        <v>82.6</v>
+      </c>
+      <c r="H10" s="2">
+        <v>51</v>
+      </c>
+      <c r="I10" s="2">
+        <v>44</v>
+      </c>
+      <c r="J10" s="3">
+        <v>52</v>
+      </c>
+      <c r="K10" t="s">
+        <v>132</v>
+      </c>
+      <c r="N10" t="str">
+        <f>_xlfn.XLOOKUP(C10, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F89</v>
+      </c>
+      <c r="O10" t="str">
+        <f>IF(D10="", "", _xlfn.XLOOKUP(D10, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201217</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="0"/>
+        <v>0.86274509803921573</v>
+      </c>
+      <c r="Q10" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>201214</v>
+      </c>
+      <c r="E11">
+        <v>20</v>
+      </c>
+      <c r="F11" s="2">
+        <v>58.8</v>
+      </c>
+      <c r="G11">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="H11" s="2">
+        <v>51</v>
+      </c>
+      <c r="I11" s="2">
+        <v>35</v>
+      </c>
+      <c r="J11" s="3">
+        <v>43</v>
+      </c>
+      <c r="K11" t="s">
+        <v>132</v>
+      </c>
+      <c r="N11" t="str">
+        <f>_xlfn.XLOOKUP(C11, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F8E</v>
+      </c>
+      <c r="O11" t="str">
+        <f>IF(D11="", "", _xlfn.XLOOKUP(D11, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201214</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="0"/>
+        <v>0.68627450980392157</v>
+      </c>
+      <c r="Q11" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12">
+        <v>21</v>
+      </c>
+      <c r="D12">
+        <v>201213</v>
+      </c>
+      <c r="E12">
+        <v>21</v>
+      </c>
+      <c r="F12" s="2">
+        <v>59</v>
+      </c>
+      <c r="G12">
+        <v>69.599999999999994</v>
+      </c>
+      <c r="H12" s="2">
+        <v>47</v>
+      </c>
+      <c r="I12" s="2">
+        <v>36</v>
+      </c>
+      <c r="J12" s="3">
+        <v>42</v>
+      </c>
+      <c r="K12" t="s">
+        <v>132</v>
+      </c>
+      <c r="N12" t="str">
+        <f>_xlfn.XLOOKUP(C12, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F88</v>
+      </c>
+      <c r="O12" t="str">
+        <f>IF(D12="", "", _xlfn.XLOOKUP(D12, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201213</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="0"/>
+        <v>0.76595744680851063</v>
+      </c>
+      <c r="Q12" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13">
+        <v>23</v>
+      </c>
+      <c r="D13">
+        <v>201225</v>
+      </c>
+      <c r="E13">
+        <v>22</v>
+      </c>
+      <c r="F13" s="2">
+        <v>63.4</v>
+      </c>
+      <c r="G13">
+        <v>75.2</v>
+      </c>
+      <c r="H13" s="2">
+        <v>46</v>
+      </c>
+      <c r="I13" s="2">
+        <v>35</v>
+      </c>
+      <c r="J13" s="3">
+        <v>43</v>
+      </c>
+      <c r="K13" t="s">
+        <v>132</v>
+      </c>
+      <c r="N13" t="str">
+        <f>_xlfn.XLOOKUP(C13, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F85</v>
+      </c>
+      <c r="O13" t="str">
+        <f>IF(D13="", "", _xlfn.XLOOKUP(D13, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201225</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="0"/>
+        <v>0.76086956521739135</v>
+      </c>
+      <c r="Q13" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14">
+        <v>24</v>
+      </c>
+      <c r="D14">
+        <v>201224</v>
+      </c>
+      <c r="E14">
+        <v>23</v>
+      </c>
+      <c r="F14" s="2">
+        <v>65.400000000000006</v>
+      </c>
+      <c r="G14">
+        <v>77</v>
+      </c>
+      <c r="H14" s="2">
+        <v>51</v>
+      </c>
+      <c r="I14" s="2">
+        <v>57</v>
+      </c>
+      <c r="J14" s="3">
+        <v>45</v>
+      </c>
+      <c r="K14" t="s">
+        <v>132</v>
+      </c>
+      <c r="N14" t="str">
+        <f>_xlfn.XLOOKUP(C14, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F68</v>
+      </c>
+      <c r="O14" t="str">
+        <f>IF(D14="", "", _xlfn.XLOOKUP(D14, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201224</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="0"/>
+        <v>1.1176470588235294</v>
+      </c>
+      <c r="Q14" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15">
+        <v>25</v>
+      </c>
+      <c r="E15">
+        <v>24</v>
+      </c>
+      <c r="F15" s="2">
+        <v>61.4</v>
+      </c>
+      <c r="G15">
+        <v>72.3</v>
+      </c>
+      <c r="H15" s="2">
+        <v>47</v>
+      </c>
+      <c r="I15" s="2">
+        <v>36</v>
+      </c>
+      <c r="J15" s="3">
+        <v>43</v>
+      </c>
+      <c r="K15" t="s">
+        <v>132</v>
+      </c>
+      <c r="N15" t="str">
+        <f>_xlfn.XLOOKUP(C15, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F69</v>
+      </c>
+      <c r="O15" t="str">
+        <f>IF(D15="", "", _xlfn.XLOOKUP(D15, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+      <c r="P15">
+        <f t="shared" si="0"/>
+        <v>0.76595744680851063</v>
+      </c>
+      <c r="Q15" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="F16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="3"/>
+      <c r="O16" t="str">
+        <f>IF(D16="", "", _xlfn.XLOOKUP(D16, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="3"/>
+      <c r="O17" t="str">
+        <f>IF(D17="", "", _xlfn.XLOOKUP(D17, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="3"/>
+      <c r="O18" t="str">
+        <f>IF(D18="", "", _xlfn.XLOOKUP(D18, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
+      <c r="O19" t="str">
+        <f>IF(D19="", "", _xlfn.XLOOKUP(D19, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="3"/>
+      <c r="O20" t="str">
+        <f>IF(D20="", "", _xlfn.XLOOKUP(D20, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="3"/>
+      <c r="O21" t="str">
+        <f>IF(D21="", "", _xlfn.XLOOKUP(D21, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="3"/>
+      <c r="O22" t="str">
+        <f>IF(D22="", "", _xlfn.XLOOKUP(D22, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="3"/>
+      <c r="O23" t="str">
+        <f>IF(D23="", "", _xlfn.XLOOKUP(D23, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="3"/>
+      <c r="O24" t="str">
+        <f>IF(D24="", "", _xlfn.XLOOKUP(D24, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="3"/>
+      <c r="O25" t="str">
+        <f>IF(D25="", "", _xlfn.XLOOKUP(D25, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="3"/>
+      <c r="O26" t="str">
+        <f>IF(D26="", "", _xlfn.XLOOKUP(D26, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="3"/>
+      <c r="O27" t="str">
+        <f>IF(D27="", "", _xlfn.XLOOKUP(D27, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="3"/>
+      <c r="O28" t="str">
+        <f>IF(D28="", "", _xlfn.XLOOKUP(D28, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="3"/>
+      <c r="O29" t="str">
+        <f>IF(D29="", "", _xlfn.XLOOKUP(D29, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="3"/>
+      <c r="O30" t="str">
+        <f>IF(D30="", "", _xlfn.XLOOKUP(D30, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="3"/>
+      <c r="O31" t="str">
+        <f>IF(D31="", "", _xlfn.XLOOKUP(D31, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="3"/>
+      <c r="O32" t="str">
+        <f>IF(D32="", "", _xlfn.XLOOKUP(D32, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="3"/>
+      <c r="O33" t="str">
+        <f>IF(D33="", "", _xlfn.XLOOKUP(D33, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="3"/>
+      <c r="O34" t="str">
+        <f>IF(D34="", "", _xlfn.XLOOKUP(D34, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="3"/>
+      <c r="O35" t="str">
+        <f>IF(D35="", "", _xlfn.XLOOKUP(D35, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="3"/>
+      <c r="O36" t="str">
+        <f>IF(D36="", "", _xlfn.XLOOKUP(D36, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="3"/>
+    </row>
+    <row r="38" spans="6:15" x14ac:dyDescent="0.35">
+      <c r="F38" s="2"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{488E39B3-2C61-459C-8BA6-3DDB189E9E40}">
   <dimension ref="A1:Y36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" customWidth="1"/>
-    <col min="17" max="17" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.54296875" customWidth="1"/>
+    <col min="10" max="10" width="7.7265625" customWidth="1"/>
+    <col min="11" max="11" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7265625" customWidth="1"/>
+    <col min="17" max="17" width="12.1796875" customWidth="1"/>
     <col min="18" max="18" width="4" customWidth="1"/>
-    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>88</v>
       </c>
@@ -5285,7 +7214,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>25</v>
       </c>
@@ -5356,7 +7285,7 @@
         <v>4948116</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>26</v>
       </c>
@@ -5407,7 +7336,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>27</v>
       </c>
@@ -5458,7 +7387,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>28</v>
       </c>
@@ -5509,7 +7438,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>29</v>
       </c>
@@ -5560,7 +7489,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>30</v>
       </c>
@@ -5611,7 +7540,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>31</v>
       </c>
@@ -5665,7 +7594,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>32</v>
       </c>
@@ -5718,7 +7647,7 @@
         <v>UKN</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>33</v>
       </c>
@@ -5771,7 +7700,7 @@
         <v>UKN</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>34</v>
       </c>
@@ -5824,7 +7753,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>35</v>
       </c>
@@ -5875,7 +7804,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>36</v>
       </c>
@@ -5926,7 +7855,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>37</v>
       </c>
@@ -5977,7 +7906,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>38</v>
       </c>
@@ -6031,7 +7960,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>39</v>
       </c>
@@ -6082,7 +8011,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="17" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N17" t="str">
         <f>IF(C17="", "", _xlfn.XLOOKUP(C17, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6092,7 +8021,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N18" t="str">
         <f>IF(C18="", "", _xlfn.XLOOKUP(C18, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6102,7 +8031,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N19" t="str">
         <f>IF(C19="", "", _xlfn.XLOOKUP(C19, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6112,7 +8041,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N20" t="str">
         <f>IF(C20="", "", _xlfn.XLOOKUP(C20, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6122,7 +8051,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N21" t="str">
         <f>IF(C21="", "", _xlfn.XLOOKUP(C21, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6132,7 +8061,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N22" t="str">
         <f>IF(C22="", "", _xlfn.XLOOKUP(C22, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6142,7 +8071,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N23" t="str">
         <f>IF(C23="", "", _xlfn.XLOOKUP(C23, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6152,7 +8081,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N24" t="str">
         <f>IF(C24="", "", _xlfn.XLOOKUP(C24, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6162,7 +8091,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N25" t="str">
         <f>IF(C25="", "", _xlfn.XLOOKUP(C25, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6172,7 +8101,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N26" t="str">
         <f>IF(C26="", "", _xlfn.XLOOKUP(C26, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6182,7 +8111,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N27" t="str">
         <f>IF(C27="", "", _xlfn.XLOOKUP(C27, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6192,7 +8121,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N28" t="str">
         <f>IF(C28="", "", _xlfn.XLOOKUP(C28, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6202,7 +8131,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N29" t="str">
         <f>IF(C29="", "", _xlfn.XLOOKUP(C29, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6212,7 +8141,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N30" t="str">
         <f>IF(C30="", "", _xlfn.XLOOKUP(C30, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6222,7 +8151,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N31" t="str">
         <f>IF(C31="", "", _xlfn.XLOOKUP(C31, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6232,7 +8161,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N32" t="str">
         <f>IF(C32="", "", _xlfn.XLOOKUP(C32, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6242,7 +8171,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N33" t="str">
         <f>IF(C33="", "", _xlfn.XLOOKUP(C33, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6252,7 +8181,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N34" t="str">
         <f>IF(C34="", "", _xlfn.XLOOKUP(C34, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6262,13 +8191,13 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N35" t="str">
         <f>IF(C35="", "", _xlfn.XLOOKUP(C35, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="14:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="14:15" x14ac:dyDescent="0.35">
       <c r="N36" t="str">
         <f>IF(C36="", "", _xlfn.XLOOKUP(C36, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -6276,13 +8205,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="Q2:Q36">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$Q2="UKN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="2" stopIfTrue="1">
       <formula>AND($Q2=$B2, $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="3" stopIfTrue="1">
       <formula>AND($Q2&lt;&gt;$B2, $Q2&lt;&gt;"UKN", $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6290,32 +8219,32 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06DEAEC3-E597-43CF-8A39-542D98AFB6F7}">
   <dimension ref="A1:Y38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" customWidth="1"/>
-    <col min="17" max="17" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.54296875" customWidth="1"/>
+    <col min="10" max="10" width="7.7265625" customWidth="1"/>
+    <col min="11" max="11" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7265625" customWidth="1"/>
+    <col min="17" max="17" width="12.1796875" customWidth="1"/>
     <col min="18" max="18" width="4" customWidth="1"/>
-    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>88</v>
       </c>
@@ -6386,7 +8315,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>40</v>
       </c>
@@ -6455,7 +8384,7 @@
         <v>4948116</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>41</v>
       </c>
@@ -6506,7 +8435,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>42</v>
       </c>
@@ -6557,7 +8486,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>43</v>
       </c>
@@ -6605,7 +8534,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>44</v>
       </c>
@@ -6653,7 +8582,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>45</v>
       </c>
@@ -6704,7 +8633,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>46</v>
       </c>
@@ -6752,7 +8681,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>47</v>
       </c>
@@ -6800,7 +8729,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>48</v>
       </c>
@@ -6851,7 +8780,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>49</v>
       </c>
@@ -6902,7 +8831,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>50</v>
       </c>
@@ -6953,7 +8882,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>51</v>
       </c>
@@ -7006,7 +8935,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -7020,7 +8949,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -7034,7 +8963,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -7048,7 +8977,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -7062,7 +8991,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -7076,7 +9005,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -7090,7 +9019,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -7104,7 +9033,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -7118,7 +9047,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -7132,7 +9061,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -7146,7 +9075,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -7160,7 +9089,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -7174,7 +9103,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -7188,7 +9117,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -7202,7 +9131,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -7216,7 +9145,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -7230,7 +9159,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -7244,7 +9173,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -7258,7 +9187,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -7272,7 +9201,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -7286,7 +9215,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -7300,7 +9229,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -7310,7 +9239,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -7320,25 +9249,25 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F38" s="2"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <conditionalFormatting sqref="Q2:Q100">
-    <cfRule type="expression" dxfId="5" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="1" stopIfTrue="1">
       <formula>AND($Q2&lt;&gt;$B2, $Q2&lt;&gt;"UKN", $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>$Q2="UKN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="3" stopIfTrue="1">
       <formula>AND($Q2=$B2, $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7346,32 +9275,32 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7092AF79-999B-48C9-8AAD-B4913AEC6A18}">
   <dimension ref="A1:Y38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" customWidth="1"/>
-    <col min="17" max="17" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.54296875" customWidth="1"/>
+    <col min="10" max="10" width="7.7265625" customWidth="1"/>
+    <col min="11" max="11" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7265625" customWidth="1"/>
+    <col min="17" max="17" width="12.1796875" customWidth="1"/>
     <col min="18" max="18" width="4" customWidth="1"/>
-    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>88</v>
       </c>
@@ -7442,7 +9371,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>52</v>
       </c>
@@ -7514,7 +9443,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>53</v>
       </c>
@@ -7570,7 +9499,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>54</v>
       </c>
@@ -7624,7 +9553,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>55</v>
       </c>
@@ -7678,7 +9607,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>56</v>
       </c>
@@ -7732,7 +9661,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>57</v>
       </c>
@@ -7783,7 +9712,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>58</v>
       </c>
@@ -7834,7 +9763,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>59</v>
       </c>
@@ -7885,7 +9814,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>60</v>
       </c>
@@ -7936,7 +9865,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>61</v>
       </c>
@@ -7987,7 +9916,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>62</v>
       </c>
@@ -8038,7 +9967,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>63</v>
       </c>
@@ -8091,7 +10020,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -8105,7 +10034,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -8119,7 +10048,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="F16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -8133,7 +10062,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -8147,7 +10076,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -8161,7 +10090,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -8175,7 +10104,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -8189,7 +10118,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -8203,7 +10132,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -8217,7 +10146,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -8231,7 +10160,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -8245,7 +10174,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -8259,7 +10188,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -8273,7 +10202,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -8287,7 +10216,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -8301,7 +10230,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -8315,7 +10244,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -8329,7 +10258,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -8343,7 +10272,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -8357,7 +10286,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -8371,7 +10300,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -8385,7 +10314,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -8395,7 +10324,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -8405,25 +10334,25 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="6:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="6:15" x14ac:dyDescent="0.35">
       <c r="F38" s="2"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <conditionalFormatting sqref="Q2:Q100">
-    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>AND($Q2&lt;&gt;$B2, $Q2&lt;&gt;"UKN", $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$Q2="UKN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>AND($Q2=$B2, $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/tagsheet_to_tidbits2025/data/Sander's PIT CODES.xlsx
+++ b/tagsheet_to_tidbits2025/data/Sander's PIT CODES.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f03cf4e0d6e7cfb9/Desktop/Code/Sturgeon_TidBits/tagsheet_to_tidbits2025/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://umainesystem-my.sharepoint.com/personal/sander_elliott_maine_edu/Documents/Desktop/Github/Sturgeon_TidBits/tagsheet_to_tidbits2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{87E30D02-C812-421C-A0AA-2F4032EB8D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C72B015-15B0-438A-B96A-E871B20D540E}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{87E30D02-C812-421C-A0AA-2F4032EB8D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D613798-27E4-42F6-8F60-023531AB6DF7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29070" yWindow="0" windowWidth="28530" windowHeight="15480" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trip" sheetId="7" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
     <sheet name="Sheet1 (2)" sheetId="13" r:id="rId3"/>
-    <sheet name="Trip(1)" sheetId="2" r:id="rId4"/>
-    <sheet name="Trip (2)" sheetId="8" r:id="rId5"/>
-    <sheet name="Trip (3)" sheetId="9" r:id="rId6"/>
-    <sheet name="Trip (4)" sheetId="11" r:id="rId7"/>
-    <sheet name="Trip (5)" sheetId="12" r:id="rId8"/>
+    <sheet name="Sheet2" sheetId="14" r:id="rId4"/>
+    <sheet name="Trip(1)" sheetId="2" r:id="rId5"/>
+    <sheet name="Trip (2)" sheetId="8" r:id="rId6"/>
+    <sheet name="Trip (3)" sheetId="9" r:id="rId7"/>
+    <sheet name="Trip (4)" sheetId="11" r:id="rId8"/>
+    <sheet name="Trip (5)" sheetId="12" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="174">
   <si>
     <t>3DD.003E185F8C</t>
   </si>
@@ -546,9 +547,6 @@
     <t>NO RIGHT PEC</t>
   </si>
   <si>
-    <t>1645258</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -561,127 +559,10 @@
     <t>V16-4x-BLU-1</t>
   </si>
   <si>
-    <t>1645259</t>
-  </si>
-  <si>
-    <t>1645260</t>
-  </si>
-  <si>
-    <t>1645261</t>
-  </si>
-  <si>
-    <t>1645262</t>
-  </si>
-  <si>
-    <t>1645263</t>
-  </si>
-  <si>
-    <t>1645264</t>
-  </si>
-  <si>
-    <t>1645265</t>
-  </si>
-  <si>
-    <t>1645266</t>
-  </si>
-  <si>
-    <t>1645267</t>
-  </si>
-  <si>
-    <t>1645268</t>
-  </si>
-  <si>
-    <t>1645269</t>
-  </si>
-  <si>
-    <t>1645270</t>
-  </si>
-  <si>
-    <t>1645271</t>
-  </si>
-  <si>
-    <t>1645272</t>
-  </si>
-  <si>
-    <t>1645273</t>
-  </si>
-  <si>
-    <t>1645274</t>
-  </si>
-  <si>
-    <t>1645275</t>
-  </si>
-  <si>
-    <t>1645276</t>
-  </si>
-  <si>
-    <t>1645277</t>
-  </si>
-  <si>
-    <t>1645278</t>
-  </si>
-  <si>
-    <t>1645279</t>
-  </si>
-  <si>
-    <t>1645280</t>
-  </si>
-  <si>
-    <t>1645281</t>
-  </si>
-  <si>
-    <t>1645282</t>
-  </si>
-  <si>
-    <t>1645283</t>
-  </si>
-  <si>
-    <t>1645284</t>
-  </si>
-  <si>
-    <t>1645285</t>
-  </si>
-  <si>
-    <t>1645286</t>
-  </si>
-  <si>
-    <t>1645287</t>
-  </si>
-  <si>
-    <t>1645288</t>
-  </si>
-  <si>
-    <t>1645289</t>
-  </si>
-  <si>
-    <t>1645290</t>
-  </si>
-  <si>
-    <t>1645291</t>
-  </si>
-  <si>
-    <t>1645292</t>
-  </si>
-  <si>
-    <t>1645293</t>
-  </si>
-  <si>
-    <t>1645294</t>
-  </si>
-  <si>
-    <t>1645295</t>
-  </si>
-  <si>
-    <t>1645296</t>
-  </si>
-  <si>
-    <t>1645297</t>
-  </si>
-  <si>
-    <t>1645298</t>
-  </si>
-  <si>
-    <t>1645299</t>
+    <t>Serial_N</t>
+  </si>
+  <si>
+    <t>V16.CODE.Full</t>
   </si>
 </sst>
 </file>
@@ -1267,7 +1148,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
@@ -1295,8 +1176,7 @@
     <xf numFmtId="0" fontId="17" fillId="13" borderId="11" xfId="22" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1344,16 +1224,6 @@
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="14">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1414,6 +1284,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1759,29 +1639,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9EDA711-86F6-489C-9871-79414856E4C9}">
   <dimension ref="A1:Y38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.54296875" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" customWidth="1"/>
-    <col min="11" max="11" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7265625" customWidth="1"/>
-    <col min="17" max="17" width="12.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" customWidth="1"/>
+    <col min="17" max="17" width="12.140625" customWidth="1"/>
     <col min="18" max="18" width="4" customWidth="1"/>
-    <col min="20" max="20" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>88</v>
       </c>
@@ -1852,7 +1732,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
       <c r="H2" s="5"/>
@@ -1879,7 +1759,7 @@
       </c>
       <c r="T2" s="1"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F3" s="2"/>
       <c r="H3" s="8"/>
       <c r="I3" s="2"/>
@@ -1897,7 +1777,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F4" s="2"/>
       <c r="H4" s="8"/>
       <c r="I4" s="2"/>
@@ -1915,7 +1795,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F5" s="2"/>
       <c r="H5" s="8"/>
       <c r="I5" s="2"/>
@@ -1933,7 +1813,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F6" s="2"/>
       <c r="H6" s="8"/>
       <c r="I6" s="2"/>
@@ -1951,7 +1831,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F7" s="2"/>
       <c r="H7" s="8"/>
       <c r="I7" s="2"/>
@@ -1969,7 +1849,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F8" s="2"/>
       <c r="H8" s="9"/>
       <c r="I8" s="2"/>
@@ -1987,7 +1867,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -2005,7 +1885,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -2023,7 +1903,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -2041,7 +1921,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -2055,7 +1935,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -2069,7 +1949,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -2083,7 +1963,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -2097,7 +1977,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -2111,7 +1991,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -2125,7 +2005,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -2139,7 +2019,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -2153,7 +2033,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -2167,7 +2047,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -2181,7 +2061,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -2195,7 +2075,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -2209,7 +2089,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -2223,7 +2103,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -2237,7 +2117,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -2251,7 +2131,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -2265,7 +2145,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -2279,7 +2159,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -2293,7 +2173,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -2307,7 +2187,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -2321,7 +2201,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -2335,7 +2215,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -2349,7 +2229,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -2363,7 +2243,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -2373,7 +2253,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -2383,13 +2263,13 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F38" s="2"/>
     </row>
   </sheetData>
@@ -2412,13 +2292,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F61"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>61</v>
       </c>
@@ -2435,7 +2315,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2453,7 +2333,7 @@
         <v>201133</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2471,7 +2351,7 @@
         <v>201127</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2489,7 +2369,7 @@
         <v>201134</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2507,7 +2387,7 @@
         <v>201128</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2525,7 +2405,7 @@
         <v>201129</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2543,7 +2423,7 @@
         <v>201131</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2561,7 +2441,7 @@
         <v>201130</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2579,7 +2459,7 @@
         <v>201132</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2597,7 +2477,7 @@
         <v>201212</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2615,7 +2495,7 @@
         <v>201215</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2633,7 +2513,7 @@
         <v>201213</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2651,7 +2531,7 @@
         <v>201214</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2669,7 +2549,7 @@
         <v>201216</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2687,7 +2567,7 @@
         <v>201217</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2705,7 +2585,7 @@
         <v>201218</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2723,7 +2603,7 @@
         <v>201219</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2741,7 +2621,7 @@
         <v>201220</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2759,7 +2639,7 @@
         <v>201223</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2777,7 +2657,7 @@
         <v>201222</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2795,7 +2675,7 @@
         <v>201221</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2813,7 +2693,7 @@
         <v>201224</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2831,7 +2711,7 @@
         <v>201225</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2849,7 +2729,7 @@
         <v>201226</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2867,7 +2747,7 @@
         <v>201227</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2885,7 +2765,7 @@
         <v>201228</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2903,7 +2783,7 @@
         <v>201229</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2921,7 +2801,7 @@
         <v>201232</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2939,7 +2819,7 @@
         <v>201231</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2957,7 +2837,7 @@
         <v>201230</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2975,7 +2855,7 @@
         <v>201235</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2993,7 +2873,7 @@
         <v>201234</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3011,7 +2891,7 @@
         <v>201233</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3029,7 +2909,7 @@
         <v>201238</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3047,7 +2927,7 @@
         <v>201237</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3065,7 +2945,7 @@
         <v>201236</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3083,7 +2963,7 @@
         <v>201239</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3101,7 +2981,7 @@
         <v>201240</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3119,7 +2999,7 @@
         <v>201241</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3137,7 +3017,7 @@
         <v>201244</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3155,7 +3035,7 @@
         <v>201243</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3173,7 +3053,7 @@
         <v>201242</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3191,7 +3071,7 @@
         <v>201247</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3209,7 +3089,7 @@
         <v>201246</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3227,7 +3107,7 @@
         <v>201245</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3245,7 +3125,7 @@
         <v>201252</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3263,7 +3143,7 @@
         <v>201249</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3281,7 +3161,7 @@
         <v>201253</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3299,7 +3179,7 @@
         <v>201250</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3317,7 +3197,7 @@
         <v>201248</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3335,7 +3215,7 @@
         <v>201251</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3343,7 +3223,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3351,7 +3231,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3359,7 +3239,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3367,7 +3247,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3375,7 +3255,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3383,7 +3263,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3391,7 +3271,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3399,7 +3279,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3407,7 +3287,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3428,14 +3308,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0019F054-F7CA-421F-8EA8-E60A6BBFF39A}">
-  <dimension ref="A1:M61"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:R61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>61</v>
       </c>
@@ -3451,8 +3332,14 @@
       <c r="F1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3469,26 +3356,14 @@
         <f>VALUE(RIGHT(E2,6))</f>
         <v>201133</v>
       </c>
-      <c r="H2" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M2" s="15" t="s">
+      <c r="H2" s="15">
+        <v>1645258</v>
+      </c>
+      <c r="I2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3505,26 +3380,23 @@
         <f t="shared" ref="F3:F51" si="0">VALUE(RIGHT(E3,6))</f>
         <v>201127</v>
       </c>
-      <c r="H3" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="I3" s="15" t="s">
+      <c r="H3" s="15">
+        <v>1645259</v>
+      </c>
+      <c r="I3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L3" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q3" t="s">
         <v>169</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="R3" t="s">
         <v>170</v>
       </c>
-      <c r="K3" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3541,26 +3413,26 @@
         <f t="shared" si="0"/>
         <v>201134</v>
       </c>
-      <c r="H4" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="I4" s="15" t="s">
+      <c r="H4" s="15">
+        <v>1645260</v>
+      </c>
+      <c r="I4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" t="s">
+        <v>171</v>
+      </c>
+      <c r="P4" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q4" t="s">
         <v>169</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="R4" t="s">
         <v>170</v>
       </c>
-      <c r="K4" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3577,26 +3449,26 @@
         <f t="shared" si="0"/>
         <v>201128</v>
       </c>
-      <c r="H5" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="I5" s="15" t="s">
+      <c r="H5" s="15">
+        <v>1645261</v>
+      </c>
+      <c r="I5" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" t="s">
+        <v>171</v>
+      </c>
+      <c r="P5" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q5" t="s">
         <v>169</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="R5" t="s">
         <v>170</v>
       </c>
-      <c r="K5" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M5" s="15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3613,26 +3485,26 @@
         <f t="shared" si="0"/>
         <v>201129</v>
       </c>
-      <c r="H6" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="I6" s="15" t="s">
+      <c r="H6" s="15">
+        <v>1645262</v>
+      </c>
+      <c r="I6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L6" t="s">
+        <v>171</v>
+      </c>
+      <c r="P6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q6" t="s">
         <v>169</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="R6" t="s">
         <v>170</v>
       </c>
-      <c r="K6" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L6" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M6" s="15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3649,26 +3521,26 @@
         <f t="shared" si="0"/>
         <v>201131</v>
       </c>
-      <c r="H7" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="I7" s="15" t="s">
+      <c r="H7" s="15">
+        <v>1645263</v>
+      </c>
+      <c r="I7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L7" t="s">
+        <v>171</v>
+      </c>
+      <c r="P7" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q7" t="s">
         <v>169</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="R7" t="s">
         <v>170</v>
       </c>
-      <c r="K7" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L7" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M7" s="15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3685,26 +3557,26 @@
         <f t="shared" si="0"/>
         <v>201130</v>
       </c>
-      <c r="H8" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="I8" s="15" t="s">
+      <c r="H8" s="15">
+        <v>1645264</v>
+      </c>
+      <c r="I8" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" t="s">
+        <v>171</v>
+      </c>
+      <c r="P8" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q8" t="s">
         <v>169</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="R8" t="s">
         <v>170</v>
       </c>
-      <c r="K8" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L8" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M8" s="15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3721,26 +3593,26 @@
         <f t="shared" si="0"/>
         <v>201132</v>
       </c>
-      <c r="H9" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="I9" s="15" t="s">
+      <c r="H9" s="15">
+        <v>1645265</v>
+      </c>
+      <c r="I9" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" t="s">
+        <v>171</v>
+      </c>
+      <c r="P9" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q9" t="s">
         <v>169</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="R9" t="s">
         <v>170</v>
       </c>
-      <c r="K9" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L9" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M9" s="15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3757,26 +3629,26 @@
         <f t="shared" si="0"/>
         <v>201212</v>
       </c>
-      <c r="H10" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="I10" s="15" t="s">
+      <c r="H10" s="15">
+        <v>1645266</v>
+      </c>
+      <c r="I10" t="s">
+        <v>80</v>
+      </c>
+      <c r="L10" t="s">
+        <v>171</v>
+      </c>
+      <c r="P10" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q10" t="s">
         <v>169</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="R10" t="s">
         <v>170</v>
       </c>
-      <c r="K10" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L10" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M10" s="15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3793,26 +3665,26 @@
         <f t="shared" si="0"/>
         <v>201215</v>
       </c>
-      <c r="H11" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="I11" s="15" t="s">
+      <c r="H11" s="15">
+        <v>1645267</v>
+      </c>
+      <c r="I11" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" t="s">
+        <v>171</v>
+      </c>
+      <c r="P11" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q11" t="s">
         <v>169</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="R11" t="s">
         <v>170</v>
       </c>
-      <c r="K11" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L11" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M11" s="15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3829,26 +3701,26 @@
         <f t="shared" si="0"/>
         <v>201213</v>
       </c>
-      <c r="H12" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="I12" s="15" t="s">
+      <c r="H12" s="15">
+        <v>1645268</v>
+      </c>
+      <c r="I12" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" t="s">
+        <v>171</v>
+      </c>
+      <c r="P12" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q12" t="s">
         <v>169</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="R12" t="s">
         <v>170</v>
       </c>
-      <c r="K12" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3865,26 +3737,26 @@
         <f t="shared" si="0"/>
         <v>201214</v>
       </c>
-      <c r="H13" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="I13" s="15" t="s">
+      <c r="H13" s="15">
+        <v>1645269</v>
+      </c>
+      <c r="I13" t="s">
+        <v>81</v>
+      </c>
+      <c r="L13" t="s">
+        <v>171</v>
+      </c>
+      <c r="P13" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q13" t="s">
         <v>169</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="R13" t="s">
         <v>170</v>
       </c>
-      <c r="K13" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L13" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M13" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3901,26 +3773,26 @@
         <f t="shared" si="0"/>
         <v>201216</v>
       </c>
-      <c r="H14" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="I14" s="15" t="s">
+      <c r="H14" s="15">
+        <v>1645270</v>
+      </c>
+      <c r="I14" t="s">
+        <v>144</v>
+      </c>
+      <c r="L14" t="s">
+        <v>171</v>
+      </c>
+      <c r="P14" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q14" t="s">
         <v>169</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="R14" t="s">
         <v>170</v>
       </c>
-      <c r="K14" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M14" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3937,26 +3809,26 @@
         <f t="shared" si="0"/>
         <v>201217</v>
       </c>
-      <c r="H15" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="I15" s="15" t="s">
+      <c r="H15" s="15">
+        <v>1645271</v>
+      </c>
+      <c r="I15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L15" t="s">
+        <v>171</v>
+      </c>
+      <c r="P15" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q15" t="s">
         <v>169</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="R15" t="s">
         <v>170</v>
       </c>
-      <c r="K15" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L15" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M15" s="15" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3973,26 +3845,26 @@
         <f t="shared" si="0"/>
         <v>201218</v>
       </c>
-      <c r="H16" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="I16" s="15" t="s">
+      <c r="H16" s="15">
+        <v>1645272</v>
+      </c>
+      <c r="I16" t="s">
+        <v>85</v>
+      </c>
+      <c r="L16" t="s">
+        <v>171</v>
+      </c>
+      <c r="P16" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q16" t="s">
         <v>169</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="R16" t="s">
         <v>170</v>
       </c>
-      <c r="K16" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L16" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M16" s="15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4009,26 +3881,26 @@
         <f t="shared" si="0"/>
         <v>201219</v>
       </c>
-      <c r="H17" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="I17" s="15" t="s">
+      <c r="H17" s="15">
+        <v>1645273</v>
+      </c>
+      <c r="I17" t="s">
+        <v>86</v>
+      </c>
+      <c r="L17" t="s">
+        <v>171</v>
+      </c>
+      <c r="P17" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q17" t="s">
         <v>169</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="R17" t="s">
         <v>170</v>
       </c>
-      <c r="K17" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L17" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M17" s="15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4045,26 +3917,26 @@
         <f t="shared" si="0"/>
         <v>201220</v>
       </c>
-      <c r="H18" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="I18" s="15" t="s">
+      <c r="H18" s="15">
+        <v>1645274</v>
+      </c>
+      <c r="I18" t="s">
+        <v>87</v>
+      </c>
+      <c r="L18" t="s">
+        <v>171</v>
+      </c>
+      <c r="P18" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q18" t="s">
         <v>169</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="R18" t="s">
         <v>170</v>
       </c>
-      <c r="K18" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L18" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M18" s="15" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4081,26 +3953,26 @@
         <f t="shared" si="0"/>
         <v>201223</v>
       </c>
-      <c r="H19" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="I19" s="15" t="s">
+      <c r="H19" s="15">
+        <v>1645275</v>
+      </c>
+      <c r="I19" t="s">
+        <v>100</v>
+      </c>
+      <c r="L19" t="s">
+        <v>171</v>
+      </c>
+      <c r="P19" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q19" t="s">
         <v>169</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="R19" t="s">
         <v>170</v>
       </c>
-      <c r="K19" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M19" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4117,26 +3989,26 @@
         <f t="shared" si="0"/>
         <v>201222</v>
       </c>
-      <c r="H20" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="I20" s="15" t="s">
+      <c r="H20" s="15">
+        <v>1645276</v>
+      </c>
+      <c r="I20" t="s">
+        <v>103</v>
+      </c>
+      <c r="L20" t="s">
+        <v>171</v>
+      </c>
+      <c r="P20" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q20" t="s">
         <v>169</v>
       </c>
-      <c r="J20" s="15" t="s">
+      <c r="R20" t="s">
         <v>170</v>
       </c>
-      <c r="K20" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M20" s="15" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4153,26 +4025,26 @@
         <f t="shared" si="0"/>
         <v>201221</v>
       </c>
-      <c r="H21" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="I21" s="15" t="s">
+      <c r="H21" s="15">
+        <v>1645277</v>
+      </c>
+      <c r="I21" t="s">
+        <v>102</v>
+      </c>
+      <c r="L21" t="s">
+        <v>171</v>
+      </c>
+      <c r="P21" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q21" t="s">
         <v>169</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="R21" t="s">
         <v>170</v>
       </c>
-      <c r="K21" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L21" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M21" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4189,26 +4061,26 @@
         <f t="shared" si="0"/>
         <v>201224</v>
       </c>
-      <c r="H22" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="I22" s="15" t="s">
+      <c r="H22" s="15">
+        <v>1645278</v>
+      </c>
+      <c r="I22" t="s">
+        <v>101</v>
+      </c>
+      <c r="L22" t="s">
+        <v>171</v>
+      </c>
+      <c r="P22" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q22" t="s">
         <v>169</v>
       </c>
-      <c r="J22" s="15" t="s">
+      <c r="R22" t="s">
         <v>170</v>
       </c>
-      <c r="K22" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L22" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M22" s="15" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4225,26 +4097,26 @@
         <f t="shared" si="0"/>
         <v>201225</v>
       </c>
-      <c r="H23" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="I23" s="15" t="s">
+      <c r="H23" s="15">
+        <v>1645279</v>
+      </c>
+      <c r="I23" t="s">
+        <v>106</v>
+      </c>
+      <c r="L23" t="s">
+        <v>171</v>
+      </c>
+      <c r="P23" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q23" t="s">
         <v>169</v>
       </c>
-      <c r="J23" s="15" t="s">
+      <c r="R23" t="s">
         <v>170</v>
       </c>
-      <c r="K23" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L23" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M23" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4261,26 +4133,26 @@
         <f t="shared" si="0"/>
         <v>201226</v>
       </c>
-      <c r="H24" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="I24" s="15" t="s">
+      <c r="H24" s="15">
+        <v>1645280</v>
+      </c>
+      <c r="I24" t="s">
+        <v>105</v>
+      </c>
+      <c r="L24" t="s">
+        <v>171</v>
+      </c>
+      <c r="P24" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q24" t="s">
         <v>169</v>
       </c>
-      <c r="J24" s="15" t="s">
+      <c r="R24" t="s">
         <v>170</v>
       </c>
-      <c r="K24" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L24" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M24" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4297,26 +4169,26 @@
         <f t="shared" si="0"/>
         <v>201227</v>
       </c>
-      <c r="H25" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="I25" s="15" t="s">
+      <c r="H25" s="15">
+        <v>1645281</v>
+      </c>
+      <c r="I25" t="s">
+        <v>104</v>
+      </c>
+      <c r="L25" t="s">
+        <v>171</v>
+      </c>
+      <c r="P25" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q25" t="s">
         <v>169</v>
       </c>
-      <c r="J25" s="15" t="s">
+      <c r="R25" t="s">
         <v>170</v>
       </c>
-      <c r="K25" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L25" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M25" s="15" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4333,26 +4205,26 @@
         <f t="shared" si="0"/>
         <v>201228</v>
       </c>
-      <c r="H26" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="I26" s="15" t="s">
+      <c r="H26" s="15">
+        <v>1645282</v>
+      </c>
+      <c r="I26" t="s">
+        <v>109</v>
+      </c>
+      <c r="L26" t="s">
+        <v>171</v>
+      </c>
+      <c r="P26" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q26" t="s">
         <v>169</v>
       </c>
-      <c r="J26" s="15" t="s">
+      <c r="R26" t="s">
         <v>170</v>
       </c>
-      <c r="K26" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L26" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M26" s="15" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4369,26 +4241,26 @@
         <f t="shared" si="0"/>
         <v>201229</v>
       </c>
-      <c r="H27" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="I27" s="15" t="s">
+      <c r="H27" s="15">
+        <v>1645283</v>
+      </c>
+      <c r="I27" t="s">
+        <v>108</v>
+      </c>
+      <c r="L27" t="s">
+        <v>171</v>
+      </c>
+      <c r="P27" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q27" t="s">
         <v>169</v>
       </c>
-      <c r="J27" s="15" t="s">
+      <c r="R27" t="s">
         <v>170</v>
       </c>
-      <c r="K27" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L27" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M27" s="15" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4405,26 +4277,26 @@
         <f t="shared" si="0"/>
         <v>201232</v>
       </c>
-      <c r="H28" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="I28" s="15" t="s">
+      <c r="H28" s="15">
+        <v>1645284</v>
+      </c>
+      <c r="I28" t="s">
+        <v>107</v>
+      </c>
+      <c r="L28" t="s">
+        <v>171</v>
+      </c>
+      <c r="P28" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q28" t="s">
         <v>169</v>
       </c>
-      <c r="J28" s="15" t="s">
+      <c r="R28" t="s">
         <v>170</v>
       </c>
-      <c r="K28" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L28" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M28" s="15" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4441,26 +4313,26 @@
         <f t="shared" si="0"/>
         <v>201231</v>
       </c>
-      <c r="H29" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="I29" s="15" t="s">
+      <c r="H29" s="15">
+        <v>1645285</v>
+      </c>
+      <c r="I29" t="s">
+        <v>110</v>
+      </c>
+      <c r="L29" t="s">
+        <v>171</v>
+      </c>
+      <c r="P29" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q29" t="s">
         <v>169</v>
       </c>
-      <c r="J29" s="15" t="s">
+      <c r="R29" t="s">
         <v>170</v>
       </c>
-      <c r="K29" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L29" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M29" s="15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4477,26 +4349,26 @@
         <f t="shared" si="0"/>
         <v>201230</v>
       </c>
-      <c r="H30" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="I30" s="15" t="s">
+      <c r="H30" s="15">
+        <v>1645286</v>
+      </c>
+      <c r="I30" t="s">
+        <v>111</v>
+      </c>
+      <c r="L30" t="s">
+        <v>171</v>
+      </c>
+      <c r="P30" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q30" t="s">
         <v>169</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="R30" t="s">
         <v>170</v>
       </c>
-      <c r="K30" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L30" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M30" s="15" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4513,26 +4385,26 @@
         <f t="shared" si="0"/>
         <v>201235</v>
       </c>
-      <c r="H31" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="I31" s="15" t="s">
+      <c r="H31" s="15">
+        <v>1645287</v>
+      </c>
+      <c r="I31" t="s">
+        <v>112</v>
+      </c>
+      <c r="L31" t="s">
+        <v>171</v>
+      </c>
+      <c r="P31" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q31" t="s">
         <v>169</v>
       </c>
-      <c r="J31" s="15" t="s">
+      <c r="R31" t="s">
         <v>170</v>
       </c>
-      <c r="K31" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L31" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M31" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4549,26 +4421,26 @@
         <f t="shared" si="0"/>
         <v>201234</v>
       </c>
-      <c r="H32" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="I32" s="15" t="s">
+      <c r="H32" s="15">
+        <v>1645288</v>
+      </c>
+      <c r="I32" t="s">
+        <v>115</v>
+      </c>
+      <c r="L32" t="s">
+        <v>171</v>
+      </c>
+      <c r="P32" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q32" t="s">
         <v>169</v>
       </c>
-      <c r="J32" s="15" t="s">
+      <c r="R32" t="s">
         <v>170</v>
       </c>
-      <c r="K32" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L32" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M32" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4585,26 +4457,26 @@
         <f t="shared" si="0"/>
         <v>201233</v>
       </c>
-      <c r="H33" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="I33" s="15" t="s">
+      <c r="H33" s="15">
+        <v>1645289</v>
+      </c>
+      <c r="I33" t="s">
+        <v>114</v>
+      </c>
+      <c r="L33" t="s">
+        <v>171</v>
+      </c>
+      <c r="P33" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q33" t="s">
         <v>169</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="R33" t="s">
         <v>170</v>
       </c>
-      <c r="K33" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L33" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M33" s="15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4621,26 +4493,26 @@
         <f t="shared" si="0"/>
         <v>201238</v>
       </c>
-      <c r="H34" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="I34" s="15" t="s">
+      <c r="H34" s="15">
+        <v>1645290</v>
+      </c>
+      <c r="I34" t="s">
+        <v>113</v>
+      </c>
+      <c r="L34" t="s">
+        <v>171</v>
+      </c>
+      <c r="P34" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q34" t="s">
         <v>169</v>
       </c>
-      <c r="J34" s="15" t="s">
+      <c r="R34" t="s">
         <v>170</v>
       </c>
-      <c r="K34" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L34" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M34" s="15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4657,26 +4529,26 @@
         <f t="shared" si="0"/>
         <v>201237</v>
       </c>
-      <c r="H35" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="I35" s="15" t="s">
+      <c r="H35" s="15">
+        <v>1645291</v>
+      </c>
+      <c r="I35" t="s">
+        <v>118</v>
+      </c>
+      <c r="L35" t="s">
+        <v>171</v>
+      </c>
+      <c r="P35" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q35" t="s">
         <v>169</v>
       </c>
-      <c r="J35" s="15" t="s">
+      <c r="R35" t="s">
         <v>170</v>
       </c>
-      <c r="K35" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L35" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M35" s="15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4693,26 +4565,26 @@
         <f t="shared" si="0"/>
         <v>201236</v>
       </c>
-      <c r="H36" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="I36" s="15" t="s">
+      <c r="H36" s="15">
+        <v>1645292</v>
+      </c>
+      <c r="I36" t="s">
+        <v>117</v>
+      </c>
+      <c r="L36" t="s">
+        <v>171</v>
+      </c>
+      <c r="P36" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q36" t="s">
         <v>169</v>
       </c>
-      <c r="J36" s="15" t="s">
+      <c r="R36" t="s">
         <v>170</v>
       </c>
-      <c r="K36" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L36" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M36" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4729,26 +4601,26 @@
         <f t="shared" si="0"/>
         <v>201239</v>
       </c>
-      <c r="H37" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="I37" s="15" t="s">
+      <c r="H37" s="15">
+        <v>1645293</v>
+      </c>
+      <c r="I37" t="s">
+        <v>116</v>
+      </c>
+      <c r="L37" t="s">
+        <v>171</v>
+      </c>
+      <c r="P37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q37" t="s">
         <v>169</v>
       </c>
-      <c r="J37" s="15" t="s">
+      <c r="R37" t="s">
         <v>170</v>
       </c>
-      <c r="K37" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L37" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M37" s="15" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4765,26 +4637,26 @@
         <f t="shared" si="0"/>
         <v>201240</v>
       </c>
-      <c r="H38" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="I38" s="15" t="s">
+      <c r="H38" s="15">
+        <v>1645294</v>
+      </c>
+      <c r="I38" t="s">
+        <v>160</v>
+      </c>
+      <c r="L38" t="s">
+        <v>171</v>
+      </c>
+      <c r="P38" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q38" t="s">
         <v>169</v>
       </c>
-      <c r="J38" s="15" t="s">
+      <c r="R38" t="s">
         <v>170</v>
       </c>
-      <c r="K38" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L38" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M38" s="15" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4801,26 +4673,26 @@
         <f t="shared" si="0"/>
         <v>201241</v>
       </c>
-      <c r="H39" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="I39" s="15" t="s">
+      <c r="H39" s="15">
+        <v>1645295</v>
+      </c>
+      <c r="I39" t="s">
+        <v>157</v>
+      </c>
+      <c r="L39" t="s">
+        <v>171</v>
+      </c>
+      <c r="P39" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q39" t="s">
         <v>169</v>
       </c>
-      <c r="J39" s="15" t="s">
+      <c r="R39" t="s">
         <v>170</v>
       </c>
-      <c r="K39" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L39" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M39" s="15" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4837,26 +4709,26 @@
         <f t="shared" si="0"/>
         <v>201244</v>
       </c>
-      <c r="H40" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="I40" s="15" t="s">
+      <c r="H40" s="15">
+        <v>1645296</v>
+      </c>
+      <c r="I40" t="s">
+        <v>159</v>
+      </c>
+      <c r="L40" t="s">
+        <v>171</v>
+      </c>
+      <c r="P40" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q40" t="s">
         <v>169</v>
       </c>
-      <c r="J40" s="15" t="s">
+      <c r="R40" t="s">
         <v>170</v>
       </c>
-      <c r="K40" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L40" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M40" s="15" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4873,26 +4745,26 @@
         <f t="shared" si="0"/>
         <v>201243</v>
       </c>
-      <c r="H41" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="I41" s="15" t="s">
+      <c r="H41" s="15">
+        <v>1645297</v>
+      </c>
+      <c r="I41" t="s">
+        <v>161</v>
+      </c>
+      <c r="L41" t="s">
+        <v>171</v>
+      </c>
+      <c r="P41" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q41" t="s">
         <v>169</v>
       </c>
-      <c r="J41" s="15" t="s">
+      <c r="R41" t="s">
         <v>170</v>
       </c>
-      <c r="K41" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L41" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M41" s="15" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4909,26 +4781,26 @@
         <f t="shared" si="0"/>
         <v>201242</v>
       </c>
-      <c r="H42" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="I42" s="15" t="s">
+      <c r="H42" s="15">
+        <v>1645298</v>
+      </c>
+      <c r="I42" t="s">
+        <v>162</v>
+      </c>
+      <c r="L42" t="s">
+        <v>171</v>
+      </c>
+      <c r="P42" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q42" t="s">
         <v>169</v>
       </c>
-      <c r="J42" s="15" t="s">
+      <c r="R42" t="s">
         <v>170</v>
       </c>
-      <c r="K42" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L42" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M42" s="15" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4945,26 +4817,26 @@
         <f t="shared" si="0"/>
         <v>201247</v>
       </c>
-      <c r="H43" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="I43" s="15" t="s">
+      <c r="H43" s="15">
+        <v>1645299</v>
+      </c>
+      <c r="I43" t="s">
+        <v>158</v>
+      </c>
+      <c r="L43" t="s">
+        <v>171</v>
+      </c>
+      <c r="P43" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q43" t="s">
         <v>169</v>
       </c>
-      <c r="J43" s="15" t="s">
+      <c r="R43" t="s">
         <v>170</v>
       </c>
-      <c r="K43" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L43" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="M43" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4981,8 +4853,23 @@
         <f t="shared" si="0"/>
         <v>201246</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H44">
+        <v>1638355</v>
+      </c>
+      <c r="I44" t="s">
+        <v>65</v>
+      </c>
+      <c r="P44" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>169</v>
+      </c>
+      <c r="R44" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4999,8 +4886,14 @@
         <f t="shared" si="0"/>
         <v>201245</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H45">
+        <v>1638356</v>
+      </c>
+      <c r="I45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5017,8 +4910,14 @@
         <f t="shared" si="0"/>
         <v>201252</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H46">
+        <v>1638357</v>
+      </c>
+      <c r="I46" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5035,8 +4934,14 @@
         <f t="shared" si="0"/>
         <v>201249</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H47">
+        <v>1638358</v>
+      </c>
+      <c r="I47" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5053,8 +4958,14 @@
         <f t="shared" si="0"/>
         <v>201253</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H48">
+        <v>1638359</v>
+      </c>
+      <c r="I48" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5071,8 +4982,14 @@
         <f t="shared" si="0"/>
         <v>201250</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H49">
+        <v>1638360</v>
+      </c>
+      <c r="I49" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5089,8 +5006,14 @@
         <f t="shared" si="0"/>
         <v>201248</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H50">
+        <v>1638361</v>
+      </c>
+      <c r="I50" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5107,8 +5030,14 @@
         <f t="shared" si="0"/>
         <v>201251</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H51">
+        <v>1638362</v>
+      </c>
+      <c r="I51" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5116,7 +5045,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5124,7 +5053,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5132,7 +5061,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5140,7 +5069,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5148,7 +5077,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5156,7 +5085,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5164,7 +5093,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5172,7 +5101,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5180,7 +5109,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5189,8 +5118,9 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="F2:F51">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5198,854 +5128,449 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FD9965-3A02-44AF-9BF4-86BFA009B4F7}">
-  <dimension ref="A1:Y38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.54296875" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" customWidth="1"/>
-    <col min="11" max="11" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.1796875" customWidth="1"/>
-    <col min="18" max="18" width="4" customWidth="1"/>
-    <col min="20" max="20" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.7265625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AE4A661-52D8-45D9-824A-E6313569953C}">
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="T1" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="U1" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="V1" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="W1" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="X1" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y1" s="14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
+        <v>1645258</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>201133</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5">
-        <v>138</v>
-      </c>
-      <c r="G2" s="6">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="15">
+        <v>1645259</v>
+      </c>
+      <c r="B3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
+        <v>1645260</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>1645261</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
+        <v>1645262</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
+        <v>1645263</v>
+      </c>
+      <c r="B7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
+        <v>1645264</v>
+      </c>
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
+        <v>1645265</v>
+      </c>
+      <c r="B9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
+        <v>1645266</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
+        <v>1645267</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="15">
+        <v>1645268</v>
+      </c>
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
+        <v>1645269</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="15">
+        <v>1645270</v>
+      </c>
+      <c r="B14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="15">
+        <v>1645271</v>
+      </c>
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="15">
+        <v>1645272</v>
+      </c>
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="15">
+        <v>1645273</v>
+      </c>
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="15">
+        <v>1645274</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
+        <v>1645275</v>
+      </c>
+      <c r="B19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="15">
+        <v>1645276</v>
+      </c>
+      <c r="B20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="15">
+        <v>1645277</v>
+      </c>
+      <c r="B21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="15">
+        <v>1645278</v>
+      </c>
+      <c r="B22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="15">
+        <v>1645279</v>
+      </c>
+      <c r="B23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="15">
+        <v>1645280</v>
+      </c>
+      <c r="B24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="15">
+        <v>1645281</v>
+      </c>
+      <c r="B25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="15">
+        <v>1645282</v>
+      </c>
+      <c r="B26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="15">
+        <v>1645283</v>
+      </c>
+      <c r="B27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="15">
+        <v>1645284</v>
+      </c>
+      <c r="B28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="15">
+        <v>1645285</v>
+      </c>
+      <c r="B29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="15">
+        <v>1645286</v>
+      </c>
+      <c r="B30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="15">
+        <v>1645287</v>
+      </c>
+      <c r="B31" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="15">
+        <v>1645288</v>
+      </c>
+      <c r="B32" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="15">
+        <v>1645289</v>
+      </c>
+      <c r="B33" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="15">
+        <v>1645290</v>
+      </c>
+      <c r="B34" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="15">
+        <v>1645291</v>
+      </c>
+      <c r="B35" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="15">
+        <v>1645292</v>
+      </c>
+      <c r="B36" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="15">
+        <v>1645293</v>
+      </c>
+      <c r="B37" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="15">
+        <v>1645294</v>
+      </c>
+      <c r="B38" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="15">
+        <v>1645295</v>
+      </c>
+      <c r="B39" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="15">
+        <v>1645296</v>
+      </c>
+      <c r="B40" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="15">
+        <v>1645297</v>
+      </c>
+      <c r="B41" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="15">
+        <v>1645298</v>
+      </c>
+      <c r="B42" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="15">
+        <v>1645299</v>
+      </c>
+      <c r="B43" t="s">
         <v>158</v>
       </c>
-      <c r="H2" s="5">
-        <v>102</v>
-      </c>
-      <c r="I2" s="5">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="J2" s="7">
-        <v>61</v>
-      </c>
-      <c r="K2" t="s">
-        <v>132</v>
-      </c>
-      <c r="N2" t="str">
-        <f>_xlfn.XLOOKUP(C2, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F8C</v>
-      </c>
-      <c r="O2" t="str">
-        <f>_xlfn.XLOOKUP(D2, Sheet1!F:F, Sheet1!E:E, "")</f>
-        <v>A69-2801-201133</v>
-      </c>
-      <c r="P2">
-        <f>IF(OR(I2="",H2=""),"",I2/H2)</f>
-        <v>0.33039215686274515</v>
-      </c>
-      <c r="Q2" t="str">
-        <f>IF(P2="", "UKN", IF(P2&lt;0.55, "AST", IF(P2&gt;0.62, "SNS", "UKN")))</f>
-        <v>AST</v>
-      </c>
-      <c r="R2" t="s">
-        <v>136</v>
-      </c>
-      <c r="T2" s="1">
-        <v>45867</v>
-      </c>
-      <c r="U2" t="s">
-        <v>124</v>
-      </c>
-      <c r="V2" t="s">
-        <v>125</v>
-      </c>
-      <c r="W2">
-        <v>438716</v>
-      </c>
-      <c r="X2">
-        <v>4899033</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>201127</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2">
-        <v>156</v>
-      </c>
-      <c r="G3">
-        <v>179</v>
-      </c>
-      <c r="H3" s="2">
-        <v>138</v>
-      </c>
-      <c r="I3" s="2">
-        <v>61</v>
-      </c>
-      <c r="J3" s="3">
-        <v>101</v>
-      </c>
-      <c r="K3" t="s">
-        <v>132</v>
-      </c>
-      <c r="N3" t="str">
-        <f>_xlfn.XLOOKUP(C3, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F8D</v>
-      </c>
-      <c r="O3" t="str">
-        <f>_xlfn.XLOOKUP(D3, Sheet1!F:F, Sheet1!E:E, "")</f>
-        <v>A69-2801-201127</v>
-      </c>
-      <c r="P3">
-        <f t="shared" ref="P3:P11" si="0">IF(OR(I3="",H3=""),"",I3/H3)</f>
-        <v>0.4420289855072464</v>
-      </c>
-      <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q11" si="1">IF(P3="", "UKN", IF(P3&lt;0.55, "AST", IF(P3&gt;0.62, "SNS", "UKN")))</f>
-        <v>AST</v>
-      </c>
-      <c r="R3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>201134</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2">
-        <v>116</v>
-      </c>
-      <c r="G4">
-        <v>179</v>
-      </c>
-      <c r="H4" s="2">
-        <v>138</v>
-      </c>
-      <c r="I4" s="2">
-        <v>41.6</v>
-      </c>
-      <c r="J4" s="3">
-        <v>71.3</v>
-      </c>
-      <c r="K4" t="s">
-        <v>132</v>
-      </c>
-      <c r="N4" t="str">
-        <f>_xlfn.XLOOKUP(C4, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F93</v>
-      </c>
-      <c r="O4" t="str">
-        <f>_xlfn.XLOOKUP(D4, Sheet1!F:F, Sheet1!E:E, "")</f>
-        <v>A69-2801-201134</v>
-      </c>
-      <c r="P4">
-        <f t="shared" si="0"/>
-        <v>0.30144927536231886</v>
-      </c>
-      <c r="Q4" t="str">
-        <f t="shared" si="1"/>
-        <v>AST</v>
-      </c>
-      <c r="R4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>201128</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2">
-        <v>174.2</v>
-      </c>
-      <c r="G5">
-        <v>194.7</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="2">
-        <v>53</v>
-      </c>
-      <c r="J5" s="3">
-        <v>87</v>
-      </c>
-      <c r="K5" t="s">
-        <v>132</v>
-      </c>
-      <c r="N5" t="str">
-        <f>_xlfn.XLOOKUP(C5, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F8F</v>
-      </c>
-      <c r="O5" t="str">
-        <f>_xlfn.XLOOKUP(D5, Sheet1!F:F, Sheet1!E:E, "")</f>
-        <v>A69-2801-201128</v>
-      </c>
-      <c r="P5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Q5" t="str">
-        <f t="shared" si="1"/>
-        <v>UKN</v>
-      </c>
-      <c r="R5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D6">
-        <v>201228</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2">
-        <v>197</v>
-      </c>
-      <c r="G6">
-        <v>225</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="2">
-        <v>74.5</v>
-      </c>
-      <c r="J6" s="3">
-        <v>102.6</v>
-      </c>
-      <c r="K6" t="s">
-        <v>131</v>
-      </c>
-      <c r="L6" t="s">
-        <v>151</v>
-      </c>
-      <c r="N6" t="s">
-        <v>130</v>
-      </c>
-      <c r="O6" t="str">
-        <f>_xlfn.XLOOKUP(D6, Sheet1!F:F, Sheet1!E:E, "")</f>
-        <v>A69-2801-201228</v>
-      </c>
-      <c r="P6" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Q6" t="str">
-        <f t="shared" si="1"/>
-        <v>UKN</v>
-      </c>
-      <c r="R6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>201131</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7" s="2">
-        <v>156.30000000000001</v>
-      </c>
-      <c r="G7">
-        <v>177.9</v>
-      </c>
-      <c r="H7" s="2">
-        <v>127.37</v>
-      </c>
-      <c r="I7" s="2">
-        <v>56.91</v>
-      </c>
-      <c r="J7" s="3">
-        <v>89.37</v>
-      </c>
-      <c r="K7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L7" t="s">
-        <v>133</v>
-      </c>
-      <c r="N7" t="str">
-        <f>_xlfn.XLOOKUP(C7, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F77</v>
-      </c>
-      <c r="O7" t="str">
-        <f>_xlfn.XLOOKUP(D7, Sheet1!F:F, Sheet1!E:E, "")</f>
-        <v>A69-2801-201131</v>
-      </c>
-      <c r="P7">
-        <f t="shared" si="0"/>
-        <v>0.44680851063829785</v>
-      </c>
-      <c r="Q7" t="str">
-        <f t="shared" si="1"/>
-        <v>AST</v>
-      </c>
-      <c r="R7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-      <c r="D8">
-        <v>201130</v>
-      </c>
-      <c r="E8">
-        <v>7</v>
-      </c>
-      <c r="F8" s="2">
-        <v>134</v>
-      </c>
-      <c r="G8">
-        <v>149.5</v>
-      </c>
-      <c r="H8" s="9">
-        <v>110.5</v>
-      </c>
-      <c r="I8" s="2">
-        <v>48.8</v>
-      </c>
-      <c r="J8" s="3">
-        <v>75.099999999999994</v>
-      </c>
-      <c r="K8" t="s">
-        <v>132</v>
-      </c>
-      <c r="N8" t="str">
-        <f>_xlfn.XLOOKUP(C8, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F76</v>
-      </c>
-      <c r="O8" t="str">
-        <f>_xlfn.XLOOKUP(D8, Sheet1!F:F, Sheet1!E:E, "")</f>
-        <v>A69-2801-201130</v>
-      </c>
-      <c r="P8">
-        <f t="shared" si="0"/>
-        <v>0.44162895927601808</v>
-      </c>
-      <c r="Q8" t="str">
-        <f t="shared" si="1"/>
-        <v>AST</v>
-      </c>
-      <c r="R8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
-      </c>
-      <c r="D9">
-        <v>201132</v>
-      </c>
-      <c r="E9">
-        <v>8</v>
-      </c>
-      <c r="F9" s="2">
-        <v>149.30000000000001</v>
-      </c>
-      <c r="G9">
-        <v>173.1</v>
-      </c>
-      <c r="H9" s="2">
-        <v>127.6</v>
-      </c>
-      <c r="I9" s="2">
-        <v>46.98</v>
-      </c>
-      <c r="J9" s="3">
-        <v>71.95</v>
-      </c>
-      <c r="K9" t="s">
-        <v>132</v>
-      </c>
-      <c r="N9" t="str">
-        <f>_xlfn.XLOOKUP(C9, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F92</v>
-      </c>
-      <c r="O9" t="str">
-        <f>_xlfn.XLOOKUP(D9, Sheet1!F:F, Sheet1!E:E, "")</f>
-        <v>A69-2801-201132</v>
-      </c>
-      <c r="P9">
-        <f t="shared" si="0"/>
-        <v>0.36818181818181817</v>
-      </c>
-      <c r="Q9" t="str">
-        <f t="shared" si="1"/>
-        <v>AST</v>
-      </c>
-      <c r="R9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10">
-        <v>9</v>
-      </c>
-      <c r="D10">
-        <v>201212</v>
-      </c>
-      <c r="E10">
-        <v>9</v>
-      </c>
-      <c r="F10" s="2">
-        <v>147</v>
-      </c>
-      <c r="G10">
-        <v>170</v>
-      </c>
-      <c r="H10" s="2">
-        <v>117.37</v>
-      </c>
-      <c r="I10" s="2">
-        <v>50.15</v>
-      </c>
-      <c r="J10" s="3">
-        <v>71.64</v>
-      </c>
-      <c r="K10" t="s">
-        <v>132</v>
-      </c>
-      <c r="L10" t="s">
-        <v>137</v>
-      </c>
-      <c r="N10" t="str">
-        <f>_xlfn.XLOOKUP(C10, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F95</v>
-      </c>
-      <c r="O10" t="str">
-        <f>_xlfn.XLOOKUP(D10, Sheet1!F:F, Sheet1!E:E, "")</f>
-        <v>A69-2801-201212</v>
-      </c>
-      <c r="P10">
-        <f t="shared" si="0"/>
-        <v>0.42728124733747974</v>
-      </c>
-      <c r="Q10" t="str">
-        <f t="shared" si="1"/>
-        <v>AST</v>
-      </c>
-      <c r="R10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-      <c r="D11">
-        <v>201215</v>
-      </c>
-      <c r="E11">
-        <v>10</v>
-      </c>
-      <c r="F11" s="2">
-        <v>143.4</v>
-      </c>
-      <c r="G11">
-        <v>166</v>
-      </c>
-      <c r="H11" s="2">
-        <v>117.2</v>
-      </c>
-      <c r="I11" s="2">
-        <v>55.6</v>
-      </c>
-      <c r="J11" s="3">
-        <v>71.2</v>
-      </c>
-      <c r="K11" t="s">
-        <v>132</v>
-      </c>
-      <c r="L11" t="s">
-        <v>137</v>
-      </c>
-      <c r="N11" t="str">
-        <f>_xlfn.XLOOKUP(C11, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F86</v>
-      </c>
-      <c r="O11" t="str">
-        <f>_xlfn.XLOOKUP(D11, Sheet1!F:F, Sheet1!E:E, "")</f>
-        <v>A69-2801-201215</v>
-      </c>
-      <c r="P11">
-        <f t="shared" si="0"/>
-        <v>0.47440273037542663</v>
-      </c>
-      <c r="Q11" t="str">
-        <f t="shared" si="1"/>
-        <v>AST</v>
-      </c>
-      <c r="R11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="F12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="F13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="F14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="F15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="F16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="3"/>
-    </row>
-    <row r="28" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="3"/>
-    </row>
-    <row r="29" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="3"/>
-    </row>
-    <row r="30" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="3"/>
-    </row>
-    <row r="31" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="3"/>
-    </row>
-    <row r="32" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="3"/>
-    </row>
-    <row r="33" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="3"/>
-    </row>
-    <row r="34" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="3"/>
-    </row>
-    <row r="35" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="3"/>
-    </row>
-    <row r="36" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="3"/>
-    </row>
-    <row r="37" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="3"/>
-    </row>
-    <row r="38" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F38" s="2"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>1638355</v>
+      </c>
+      <c r="B44" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>1638356</v>
+      </c>
+      <c r="B45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1638357</v>
+      </c>
+      <c r="B46" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1638358</v>
+      </c>
+      <c r="B47" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1638359</v>
+      </c>
+      <c r="B48" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>1638360</v>
+      </c>
+      <c r="B49" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>1638361</v>
+      </c>
+      <c r="B50" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1638362</v>
+      </c>
+      <c r="B51" t="s">
+        <v>66</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83D4C17-C0AD-48BE-80DF-6BA497415298}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FD9965-3A02-44AF-9BF4-86BFA009B4F7}">
   <dimension ref="A1:Y38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.54296875" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" customWidth="1"/>
-    <col min="11" max="11" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6" customWidth="1"/>
-    <col min="17" max="17" width="12.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.140625" customWidth="1"/>
     <col min="18" max="18" width="4" customWidth="1"/>
-    <col min="20" max="20" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>88</v>
       </c>
@@ -6116,1000 +5641,725 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>201219</v>
+        <v>201133</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F2" s="5">
-        <v>73.099999999999994</v>
+        <v>138</v>
       </c>
       <c r="G2" s="6">
-        <v>88.2</v>
+        <v>158</v>
       </c>
       <c r="H2" s="5">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="I2" s="5">
-        <v>36</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="J2" s="7">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="K2" t="s">
         <v>132</v>
       </c>
       <c r="N2" t="str">
         <f>_xlfn.XLOOKUP(C2, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F7F</v>
+        <v>3DD.003E185F8C</v>
       </c>
       <c r="O2" t="str">
-        <f>IF(D2="", "", _xlfn.XLOOKUP(D2, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201219</v>
+        <f>_xlfn.XLOOKUP(D2, Sheet1!F:F, Sheet1!E:E, "")</f>
+        <v>A69-2801-201133</v>
       </c>
       <c r="P2">
         <f>IF(OR(I2="",H2=""),"",I2/H2)</f>
-        <v>0.66666666666666663</v>
+        <v>0.33039215686274515</v>
       </c>
       <c r="Q2" t="str">
         <f>IF(P2="", "UKN", IF(P2&lt;0.55, "AST", IF(P2&gt;0.62, "SNS", "UKN")))</f>
-        <v>SNS</v>
+        <v>AST</v>
       </c>
       <c r="R2" t="s">
         <v>136</v>
       </c>
       <c r="T2" s="1">
-        <v>45873</v>
+        <v>45867</v>
       </c>
       <c r="U2" t="s">
         <v>124</v>
       </c>
       <c r="V2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="W2">
-        <v>437291</v>
+        <v>438716</v>
       </c>
       <c r="X2">
-        <v>4902372</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+        <v>4899033</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>201218</v>
+        <v>201127</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>68.900000000000006</v>
+        <v>156</v>
       </c>
       <c r="G3">
-        <v>82.8</v>
-      </c>
-      <c r="H3" s="8">
-        <v>57</v>
+        <v>179</v>
+      </c>
+      <c r="H3" s="2">
+        <v>138</v>
       </c>
       <c r="I3" s="2">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="J3" s="3">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="K3" t="s">
         <v>132</v>
       </c>
       <c r="N3" t="str">
         <f>_xlfn.XLOOKUP(C3, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F94</v>
+        <v>3DD.003E185F8D</v>
       </c>
       <c r="O3" t="str">
-        <f>IF(D3="", "", _xlfn.XLOOKUP(D3, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201218</v>
+        <f>_xlfn.XLOOKUP(D3, Sheet1!F:F, Sheet1!E:E, "")</f>
+        <v>A69-2801-201127</v>
       </c>
       <c r="P3">
-        <f t="shared" ref="P3:P15" si="0">IF(OR(I3="",H3=""),"",I3/H3)</f>
-        <v>0.66666666666666663</v>
+        <f t="shared" ref="P3:P11" si="0">IF(OR(I3="",H3=""),"",I3/H3)</f>
+        <v>0.4420289855072464</v>
       </c>
       <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q15" si="1">IF(P3="", "UKN", IF(P3&lt;0.55, "AST", IF(P3&gt;0.62, "SNS", "UKN")))</f>
-        <v>SNS</v>
+        <f t="shared" ref="Q3:Q11" si="1">IF(P3="", "UKN", IF(P3&lt;0.55, "AST", IF(P3&gt;0.62, "SNS", "UKN")))</f>
+        <v>AST</v>
       </c>
       <c r="R3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="C4">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>201216</v>
+        <v>201134</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>65.599999999999994</v>
+        <v>116</v>
       </c>
       <c r="G4">
-        <v>76.599999999999994</v>
-      </c>
-      <c r="H4" s="8">
-        <v>51</v>
+        <v>179</v>
+      </c>
+      <c r="H4" s="2">
+        <v>138</v>
       </c>
       <c r="I4" s="2">
-        <v>40</v>
+        <v>41.6</v>
       </c>
       <c r="J4" s="3">
-        <v>47</v>
+        <v>71.3</v>
       </c>
       <c r="K4" t="s">
         <v>132</v>
       </c>
       <c r="N4" t="str">
         <f>_xlfn.XLOOKUP(C4, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F74</v>
+        <v>3DD.003E185F93</v>
       </c>
       <c r="O4" t="str">
-        <f>IF(D4="", "", _xlfn.XLOOKUP(D4, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201216</v>
+        <f>_xlfn.XLOOKUP(D4, Sheet1!F:F, Sheet1!E:E, "")</f>
+        <v>A69-2801-201134</v>
       </c>
       <c r="P4">
         <f t="shared" si="0"/>
-        <v>0.78431372549019607</v>
+        <v>0.30144927536231886</v>
       </c>
       <c r="Q4" t="str">
         <f t="shared" si="1"/>
-        <v>SNS</v>
+        <v>AST</v>
       </c>
       <c r="R4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="C5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>201221</v>
+        <v>201128</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>75.8</v>
+        <v>174.2</v>
       </c>
       <c r="G5">
-        <v>86.2</v>
-      </c>
-      <c r="H5" s="8">
-        <v>59</v>
-      </c>
+        <v>194.7</v>
+      </c>
+      <c r="H5" s="4"/>
       <c r="I5" s="2">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J5" s="3">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s">
         <v>132</v>
       </c>
-      <c r="L5" t="s">
-        <v>167</v>
-      </c>
       <c r="N5" t="str">
         <f>_xlfn.XLOOKUP(C5, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F91</v>
+        <v>3DD.003E185F8F</v>
       </c>
       <c r="O5" t="str">
-        <f>IF(D5="", "", _xlfn.XLOOKUP(D5, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201221</v>
-      </c>
-      <c r="P5">
-        <f t="shared" si="0"/>
-        <v>0.77966101694915257</v>
+        <f>_xlfn.XLOOKUP(D5, Sheet1!F:F, Sheet1!E:E, "")</f>
+        <v>A69-2801-201128</v>
+      </c>
+      <c r="P5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="Q5" t="str">
         <f t="shared" si="1"/>
-        <v>SNS</v>
+        <v>UKN</v>
       </c>
       <c r="R5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
+        <v>97</v>
+      </c>
+      <c r="C6" t="s">
+        <v>134</v>
       </c>
       <c r="D6">
-        <v>201220</v>
+        <v>201228</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>65.2</v>
+        <v>197</v>
       </c>
       <c r="G6">
-        <v>77.099999999999994</v>
-      </c>
-      <c r="H6" s="8">
-        <v>50</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="H6" s="4"/>
       <c r="I6" s="2">
-        <v>36</v>
+        <v>74.5</v>
       </c>
       <c r="J6" s="3">
-        <v>43</v>
+        <v>102.6</v>
       </c>
       <c r="K6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L6" t="s">
-        <v>142</v>
-      </c>
-      <c r="N6" t="str">
-        <f>_xlfn.XLOOKUP(C6, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F90</v>
+        <v>151</v>
+      </c>
+      <c r="N6" t="s">
+        <v>130</v>
       </c>
       <c r="O6" t="str">
-        <f>IF(D6="", "", _xlfn.XLOOKUP(D6, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201220</v>
-      </c>
-      <c r="P6">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <f>_xlfn.XLOOKUP(D6, Sheet1!F:F, Sheet1!E:E, "")</f>
+        <v>A69-2801-201228</v>
+      </c>
+      <c r="P6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="Q6" t="str">
         <f t="shared" si="1"/>
-        <v>SNS</v>
+        <v>UKN</v>
       </c>
       <c r="R6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="C7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>201129</v>
+        <v>201131</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
-        <v>74</v>
+        <v>156.30000000000001</v>
       </c>
       <c r="G7">
-        <v>84.8</v>
-      </c>
-      <c r="H7" s="8">
-        <v>57</v>
+        <v>177.9</v>
+      </c>
+      <c r="H7" s="2">
+        <v>127.37</v>
       </c>
       <c r="I7" s="2">
-        <v>44</v>
+        <v>56.91</v>
       </c>
       <c r="J7" s="3">
-        <v>55</v>
+        <v>89.37</v>
       </c>
       <c r="K7" t="s">
         <v>132</v>
       </c>
       <c r="L7" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="N7" t="str">
         <f>_xlfn.XLOOKUP(C7, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F78</v>
+        <v>3DD.003E185F77</v>
       </c>
       <c r="O7" t="str">
-        <f>IF(D7="", "", _xlfn.XLOOKUP(D7, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201129</v>
+        <f>_xlfn.XLOOKUP(D7, Sheet1!F:F, Sheet1!E:E, "")</f>
+        <v>A69-2801-201131</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>0.77192982456140347</v>
+        <v>0.44680851063829785</v>
       </c>
       <c r="Q7" t="str">
         <f t="shared" si="1"/>
-        <v>SNS</v>
+        <v>AST</v>
       </c>
       <c r="R7" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>201223</v>
+        <v>201130</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2">
-        <v>65.8</v>
+        <v>134</v>
       </c>
       <c r="G8">
-        <v>76.8</v>
+        <v>149.5</v>
       </c>
       <c r="H8" s="9">
-        <v>49</v>
+        <v>110.5</v>
       </c>
       <c r="I8" s="2">
-        <v>37</v>
+        <v>48.8</v>
       </c>
       <c r="J8" s="3">
-        <v>46</v>
+        <v>75.099999999999994</v>
       </c>
       <c r="K8" t="s">
         <v>132</v>
       </c>
       <c r="N8" t="str">
         <f>_xlfn.XLOOKUP(C8, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F87</v>
+        <v>3DD.003E185F76</v>
       </c>
       <c r="O8" t="str">
-        <f>IF(D8="", "", _xlfn.XLOOKUP(D8, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201223</v>
+        <f>_xlfn.XLOOKUP(D8, Sheet1!F:F, Sheet1!E:E, "")</f>
+        <v>A69-2801-201130</v>
       </c>
       <c r="P8">
         <f t="shared" si="0"/>
-        <v>0.75510204081632648</v>
+        <v>0.44162895927601808</v>
       </c>
       <c r="Q8" t="str">
         <f t="shared" si="1"/>
-        <v>SNS</v>
+        <v>AST</v>
       </c>
       <c r="R8" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="C9">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>201222</v>
+        <v>201132</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2">
-        <v>70.599999999999994</v>
+        <v>149.30000000000001</v>
       </c>
       <c r="G9">
-        <v>82.6</v>
+        <v>173.1</v>
       </c>
       <c r="H9" s="2">
-        <v>52</v>
+        <v>127.6</v>
       </c>
       <c r="I9" s="2">
-        <v>44</v>
+        <v>46.98</v>
       </c>
       <c r="J9" s="3">
-        <v>51</v>
+        <v>71.95</v>
       </c>
       <c r="K9" t="s">
         <v>132</v>
       </c>
       <c r="N9" t="str">
         <f>_xlfn.XLOOKUP(C9, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F6C</v>
+        <v>3DD.003E185F92</v>
       </c>
       <c r="O9" t="str">
-        <f>IF(D9="", "", _xlfn.XLOOKUP(D9, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201222</v>
+        <f>_xlfn.XLOOKUP(D9, Sheet1!F:F, Sheet1!E:E, "")</f>
+        <v>A69-2801-201132</v>
       </c>
       <c r="P9">
         <f t="shared" si="0"/>
-        <v>0.84615384615384615</v>
+        <v>0.36818181818181817</v>
       </c>
       <c r="Q9" t="str">
         <f t="shared" si="1"/>
-        <v>SNS</v>
+        <v>AST</v>
       </c>
       <c r="R9" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="C10">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D10">
-        <v>201217</v>
+        <v>201212</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F10" s="2">
-        <v>68.2</v>
+        <v>147</v>
       </c>
       <c r="G10">
-        <v>82.6</v>
+        <v>170</v>
       </c>
       <c r="H10" s="2">
-        <v>51</v>
+        <v>117.37</v>
       </c>
       <c r="I10" s="2">
-        <v>44</v>
+        <v>50.15</v>
       </c>
       <c r="J10" s="3">
-        <v>52</v>
+        <v>71.64</v>
       </c>
       <c r="K10" t="s">
         <v>132</v>
       </c>
+      <c r="L10" t="s">
+        <v>137</v>
+      </c>
       <c r="N10" t="str">
         <f>_xlfn.XLOOKUP(C10, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F89</v>
+        <v>3DD.003E185F95</v>
       </c>
       <c r="O10" t="str">
-        <f>IF(D10="", "", _xlfn.XLOOKUP(D10, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201217</v>
+        <f>_xlfn.XLOOKUP(D10, Sheet1!F:F, Sheet1!E:E, "")</f>
+        <v>A69-2801-201212</v>
       </c>
       <c r="P10">
         <f t="shared" si="0"/>
-        <v>0.86274509803921573</v>
+        <v>0.42728124733747974</v>
       </c>
       <c r="Q10" t="str">
         <f t="shared" si="1"/>
-        <v>SNS</v>
+        <v>AST</v>
       </c>
       <c r="R10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="C11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D11">
-        <v>201214</v>
+        <v>201215</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2">
-        <v>58.8</v>
+        <v>143.4</v>
       </c>
       <c r="G11">
-        <v>70.400000000000006</v>
+        <v>166</v>
       </c>
       <c r="H11" s="2">
-        <v>51</v>
+        <v>117.2</v>
       </c>
       <c r="I11" s="2">
-        <v>35</v>
+        <v>55.6</v>
       </c>
       <c r="J11" s="3">
-        <v>43</v>
+        <v>71.2</v>
       </c>
       <c r="K11" t="s">
         <v>132</v>
       </c>
+      <c r="L11" t="s">
+        <v>137</v>
+      </c>
       <c r="N11" t="str">
         <f>_xlfn.XLOOKUP(C11, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F8E</v>
+        <v>3DD.003E185F86</v>
       </c>
       <c r="O11" t="str">
-        <f>IF(D11="", "", _xlfn.XLOOKUP(D11, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201214</v>
+        <f>_xlfn.XLOOKUP(D11, Sheet1!F:F, Sheet1!E:E, "")</f>
+        <v>A69-2801-201215</v>
       </c>
       <c r="P11">
         <f t="shared" si="0"/>
-        <v>0.68627450980392157</v>
+        <v>0.47440273037542663</v>
       </c>
       <c r="Q11" t="str">
         <f t="shared" si="1"/>
-        <v>SNS</v>
+        <v>AST</v>
       </c>
       <c r="R11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12">
-        <v>21</v>
-      </c>
-      <c r="D12">
-        <v>201213</v>
-      </c>
-      <c r="E12">
-        <v>21</v>
-      </c>
-      <c r="F12" s="2">
-        <v>59</v>
-      </c>
-      <c r="G12">
-        <v>69.599999999999994</v>
-      </c>
-      <c r="H12" s="2">
-        <v>47</v>
-      </c>
-      <c r="I12" s="2">
-        <v>36</v>
-      </c>
-      <c r="J12" s="3">
-        <v>42</v>
-      </c>
-      <c r="K12" t="s">
-        <v>132</v>
-      </c>
-      <c r="N12" t="str">
-        <f>_xlfn.XLOOKUP(C12, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F88</v>
-      </c>
-      <c r="O12" t="str">
-        <f>IF(D12="", "", _xlfn.XLOOKUP(D12, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201213</v>
-      </c>
-      <c r="P12">
-        <f t="shared" si="0"/>
-        <v>0.76595744680851063</v>
-      </c>
-      <c r="Q12" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C13">
-        <v>23</v>
-      </c>
-      <c r="D13">
-        <v>201225</v>
-      </c>
-      <c r="E13">
-        <v>22</v>
-      </c>
-      <c r="F13" s="2">
-        <v>63.4</v>
-      </c>
-      <c r="G13">
-        <v>75.2</v>
-      </c>
-      <c r="H13" s="2">
-        <v>46</v>
-      </c>
-      <c r="I13" s="2">
-        <v>35</v>
-      </c>
-      <c r="J13" s="3">
-        <v>43</v>
-      </c>
-      <c r="K13" t="s">
-        <v>132</v>
-      </c>
-      <c r="N13" t="str">
-        <f>_xlfn.XLOOKUP(C13, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F85</v>
-      </c>
-      <c r="O13" t="str">
-        <f>IF(D13="", "", _xlfn.XLOOKUP(D13, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201225</v>
-      </c>
-      <c r="P13">
-        <f t="shared" si="0"/>
-        <v>0.76086956521739135</v>
-      </c>
-      <c r="Q13" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R13" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14">
-        <v>24</v>
-      </c>
-      <c r="D14">
-        <v>201224</v>
-      </c>
-      <c r="E14">
-        <v>23</v>
-      </c>
-      <c r="F14" s="2">
-        <v>65.400000000000006</v>
-      </c>
-      <c r="G14">
-        <v>77</v>
-      </c>
-      <c r="H14" s="2">
-        <v>51</v>
-      </c>
-      <c r="I14" s="2">
-        <v>57</v>
-      </c>
-      <c r="J14" s="3">
-        <v>45</v>
-      </c>
-      <c r="K14" t="s">
-        <v>132</v>
-      </c>
-      <c r="N14" t="str">
-        <f>_xlfn.XLOOKUP(C14, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F68</v>
-      </c>
-      <c r="O14" t="str">
-        <f>IF(D14="", "", _xlfn.XLOOKUP(D14, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v>A69-2801-201224</v>
-      </c>
-      <c r="P14">
-        <f t="shared" si="0"/>
-        <v>1.1176470588235294</v>
-      </c>
-      <c r="Q14" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s">
-        <v>140</v>
-      </c>
-      <c r="C15">
-        <v>25</v>
-      </c>
-      <c r="E15">
-        <v>24</v>
-      </c>
-      <c r="F15" s="2">
-        <v>61.4</v>
-      </c>
-      <c r="G15">
-        <v>72.3</v>
-      </c>
-      <c r="H15" s="2">
-        <v>47</v>
-      </c>
-      <c r="I15" s="2">
-        <v>36</v>
-      </c>
-      <c r="J15" s="3">
-        <v>43</v>
-      </c>
-      <c r="K15" t="s">
-        <v>132</v>
-      </c>
-      <c r="N15" t="str">
-        <f>_xlfn.XLOOKUP(C15, Sheet1!A:A, Sheet1!B:B, "")</f>
-        <v>3DD.003E185F69</v>
-      </c>
-      <c r="O15" t="str">
-        <f>IF(D15="", "", _xlfn.XLOOKUP(D15, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-      <c r="P15">
-        <f t="shared" si="0"/>
-        <v>0.76595744680851063</v>
-      </c>
-      <c r="Q15" t="str">
-        <f t="shared" si="1"/>
-        <v>SNS</v>
-      </c>
-      <c r="R15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="F12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="F13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="F14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="F15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="3"/>
-      <c r="O16" t="str">
-        <f>IF(D16="", "", _xlfn.XLOOKUP(D16, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="3"/>
-      <c r="O17" t="str">
-        <f>IF(D17="", "", _xlfn.XLOOKUP(D17, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="3"/>
-      <c r="O18" t="str">
-        <f>IF(D18="", "", _xlfn.XLOOKUP(D18, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="3"/>
-      <c r="O19" t="str">
-        <f>IF(D19="", "", _xlfn.XLOOKUP(D19, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="3"/>
-      <c r="O20" t="str">
-        <f>IF(D20="", "", _xlfn.XLOOKUP(D20, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="3"/>
-      <c r="O21" t="str">
-        <f>IF(D21="", "", _xlfn.XLOOKUP(D21, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="3"/>
-      <c r="O22" t="str">
-        <f>IF(D22="", "", _xlfn.XLOOKUP(D22, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="3"/>
-      <c r="O23" t="str">
-        <f>IF(D23="", "", _xlfn.XLOOKUP(D23, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="3"/>
-      <c r="O24" t="str">
-        <f>IF(D24="", "", _xlfn.XLOOKUP(D24, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="3"/>
-      <c r="O25" t="str">
-        <f>IF(D25="", "", _xlfn.XLOOKUP(D25, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="3"/>
-      <c r="O26" t="str">
-        <f>IF(D26="", "", _xlfn.XLOOKUP(D26, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="3"/>
-      <c r="O27" t="str">
-        <f>IF(D27="", "", _xlfn.XLOOKUP(D27, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="3"/>
-      <c r="O28" t="str">
-        <f>IF(D28="", "", _xlfn.XLOOKUP(D28, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="3"/>
-      <c r="O29" t="str">
-        <f>IF(D29="", "", _xlfn.XLOOKUP(D29, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="3"/>
-      <c r="O30" t="str">
-        <f>IF(D30="", "", _xlfn.XLOOKUP(D30, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="3"/>
-      <c r="O31" t="str">
-        <f>IF(D31="", "", _xlfn.XLOOKUP(D31, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="3"/>
-      <c r="O32" t="str">
-        <f>IF(D32="", "", _xlfn.XLOOKUP(D32, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="3"/>
-      <c r="O33" t="str">
-        <f>IF(D33="", "", _xlfn.XLOOKUP(D33, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="3"/>
-      <c r="O34" t="str">
-        <f>IF(D34="", "", _xlfn.XLOOKUP(D34, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="3"/>
-      <c r="O35" t="str">
-        <f>IF(D35="", "", _xlfn.XLOOKUP(D35, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="3"/>
-      <c r="O36" t="str">
-        <f>IF(D36="", "", _xlfn.XLOOKUP(D36, Sheet1!F:F, Sheet1!E:E, ""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="6:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F38" s="2"/>
     </row>
   </sheetData>
@@ -7119,31 +6369,1129 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83D4C17-C0AD-48BE-80DF-6BA497415298}">
+  <dimension ref="A1:Y38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6" customWidth="1"/>
+    <col min="17" max="17" width="12.140625" customWidth="1"/>
+    <col min="18" max="18" width="4" customWidth="1"/>
+    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="T1" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="U1" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="V1" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="W1" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="X1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y1" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2">
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <v>201219</v>
+      </c>
+      <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2" s="5">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="G2" s="6">
+        <v>88.2</v>
+      </c>
+      <c r="H2" s="5">
+        <v>54</v>
+      </c>
+      <c r="I2" s="5">
+        <v>36</v>
+      </c>
+      <c r="J2" s="7">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N2" t="str">
+        <f>_xlfn.XLOOKUP(C2, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F7F</v>
+      </c>
+      <c r="O2" t="str">
+        <f>IF(D2="", "", _xlfn.XLOOKUP(D2, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201219</v>
+      </c>
+      <c r="P2">
+        <f>IF(OR(I2="",H2=""),"",I2/H2)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Q2" t="str">
+        <f>IF(P2="", "UKN", IF(P2&lt;0.55, "AST", IF(P2&gt;0.62, "SNS", "UKN")))</f>
+        <v>SNS</v>
+      </c>
+      <c r="R2" t="s">
+        <v>136</v>
+      </c>
+      <c r="T2" s="1">
+        <v>45873</v>
+      </c>
+      <c r="U2" t="s">
+        <v>124</v>
+      </c>
+      <c r="V2" t="s">
+        <v>139</v>
+      </c>
+      <c r="W2">
+        <v>437291</v>
+      </c>
+      <c r="X2">
+        <v>4902372</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>201218</v>
+      </c>
+      <c r="E3">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="G3">
+        <v>82.8</v>
+      </c>
+      <c r="H3" s="8">
+        <v>57</v>
+      </c>
+      <c r="I3" s="2">
+        <v>38</v>
+      </c>
+      <c r="J3" s="3">
+        <v>46</v>
+      </c>
+      <c r="K3" t="s">
+        <v>132</v>
+      </c>
+      <c r="N3" t="str">
+        <f>_xlfn.XLOOKUP(C3, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F94</v>
+      </c>
+      <c r="O3" t="str">
+        <f>IF(D3="", "", _xlfn.XLOOKUP(D3, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201218</v>
+      </c>
+      <c r="P3">
+        <f t="shared" ref="P3:P15" si="0">IF(OR(I3="",H3=""),"",I3/H3)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Q3" t="str">
+        <f t="shared" ref="Q3:Q15" si="1">IF(P3="", "UKN", IF(P3&lt;0.55, "AST", IF(P3&gt;0.62, "SNS", "UKN")))</f>
+        <v>SNS</v>
+      </c>
+      <c r="R3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4">
+        <v>13</v>
+      </c>
+      <c r="D4">
+        <v>201216</v>
+      </c>
+      <c r="E4">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="G4">
+        <v>76.599999999999994</v>
+      </c>
+      <c r="H4" s="8">
+        <v>51</v>
+      </c>
+      <c r="I4" s="2">
+        <v>40</v>
+      </c>
+      <c r="J4" s="3">
+        <v>47</v>
+      </c>
+      <c r="K4" t="s">
+        <v>132</v>
+      </c>
+      <c r="N4" t="str">
+        <f>_xlfn.XLOOKUP(C4, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F74</v>
+      </c>
+      <c r="O4" t="str">
+        <f>IF(D4="", "", _xlfn.XLOOKUP(D4, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201216</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="0"/>
+        <v>0.78431372549019607</v>
+      </c>
+      <c r="Q4" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>201221</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2">
+        <v>75.8</v>
+      </c>
+      <c r="G5">
+        <v>86.2</v>
+      </c>
+      <c r="H5" s="8">
+        <v>59</v>
+      </c>
+      <c r="I5" s="2">
+        <v>46</v>
+      </c>
+      <c r="J5" s="3">
+        <v>54</v>
+      </c>
+      <c r="K5" t="s">
+        <v>132</v>
+      </c>
+      <c r="L5" t="s">
+        <v>167</v>
+      </c>
+      <c r="N5" t="str">
+        <f>_xlfn.XLOOKUP(C5, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F91</v>
+      </c>
+      <c r="O5" t="str">
+        <f>IF(D5="", "", _xlfn.XLOOKUP(D5, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201221</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="0"/>
+        <v>0.77966101694915257</v>
+      </c>
+      <c r="Q5" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>201220</v>
+      </c>
+      <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2">
+        <v>65.2</v>
+      </c>
+      <c r="G6">
+        <v>77.099999999999994</v>
+      </c>
+      <c r="H6" s="8">
+        <v>50</v>
+      </c>
+      <c r="I6" s="2">
+        <v>36</v>
+      </c>
+      <c r="J6" s="3">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>132</v>
+      </c>
+      <c r="L6" t="s">
+        <v>142</v>
+      </c>
+      <c r="N6" t="str">
+        <f>_xlfn.XLOOKUP(C6, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F90</v>
+      </c>
+      <c r="O6" t="str">
+        <f>IF(D6="", "", _xlfn.XLOOKUP(D6, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201220</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
+      <c r="Q6" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>201129</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2">
+        <v>74</v>
+      </c>
+      <c r="G7">
+        <v>84.8</v>
+      </c>
+      <c r="H7" s="8">
+        <v>57</v>
+      </c>
+      <c r="I7" s="2">
+        <v>44</v>
+      </c>
+      <c r="J7" s="3">
+        <v>55</v>
+      </c>
+      <c r="K7" t="s">
+        <v>132</v>
+      </c>
+      <c r="L7" t="s">
+        <v>143</v>
+      </c>
+      <c r="N7" t="str">
+        <f>_xlfn.XLOOKUP(C7, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F78</v>
+      </c>
+      <c r="O7" t="str">
+        <f>IF(D7="", "", _xlfn.XLOOKUP(D7, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201129</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="0"/>
+        <v>0.77192982456140347</v>
+      </c>
+      <c r="Q7" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>201223</v>
+      </c>
+      <c r="E8">
+        <v>17</v>
+      </c>
+      <c r="F8" s="2">
+        <v>65.8</v>
+      </c>
+      <c r="G8">
+        <v>76.8</v>
+      </c>
+      <c r="H8" s="9">
+        <v>49</v>
+      </c>
+      <c r="I8" s="2">
+        <v>37</v>
+      </c>
+      <c r="J8" s="3">
+        <v>46</v>
+      </c>
+      <c r="K8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N8" t="str">
+        <f>_xlfn.XLOOKUP(C8, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F87</v>
+      </c>
+      <c r="O8" t="str">
+        <f>IF(D8="", "", _xlfn.XLOOKUP(D8, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201223</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>0.75510204081632648</v>
+      </c>
+      <c r="Q8" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9">
+        <v>18</v>
+      </c>
+      <c r="D9">
+        <v>201222</v>
+      </c>
+      <c r="E9">
+        <v>18</v>
+      </c>
+      <c r="F9" s="2">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="G9">
+        <v>82.6</v>
+      </c>
+      <c r="H9" s="2">
+        <v>52</v>
+      </c>
+      <c r="I9" s="2">
+        <v>44</v>
+      </c>
+      <c r="J9" s="3">
+        <v>51</v>
+      </c>
+      <c r="K9" t="s">
+        <v>132</v>
+      </c>
+      <c r="N9" t="str">
+        <f>_xlfn.XLOOKUP(C9, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F6C</v>
+      </c>
+      <c r="O9" t="str">
+        <f>IF(D9="", "", _xlfn.XLOOKUP(D9, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201222</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="0"/>
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Q9" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10">
+        <v>19</v>
+      </c>
+      <c r="D10">
+        <v>201217</v>
+      </c>
+      <c r="E10">
+        <v>19</v>
+      </c>
+      <c r="F10" s="2">
+        <v>68.2</v>
+      </c>
+      <c r="G10">
+        <v>82.6</v>
+      </c>
+      <c r="H10" s="2">
+        <v>51</v>
+      </c>
+      <c r="I10" s="2">
+        <v>44</v>
+      </c>
+      <c r="J10" s="3">
+        <v>52</v>
+      </c>
+      <c r="K10" t="s">
+        <v>132</v>
+      </c>
+      <c r="N10" t="str">
+        <f>_xlfn.XLOOKUP(C10, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F89</v>
+      </c>
+      <c r="O10" t="str">
+        <f>IF(D10="", "", _xlfn.XLOOKUP(D10, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201217</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="0"/>
+        <v>0.86274509803921573</v>
+      </c>
+      <c r="Q10" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>201214</v>
+      </c>
+      <c r="E11">
+        <v>20</v>
+      </c>
+      <c r="F11" s="2">
+        <v>58.8</v>
+      </c>
+      <c r="G11">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="H11" s="2">
+        <v>51</v>
+      </c>
+      <c r="I11" s="2">
+        <v>35</v>
+      </c>
+      <c r="J11" s="3">
+        <v>43</v>
+      </c>
+      <c r="K11" t="s">
+        <v>132</v>
+      </c>
+      <c r="N11" t="str">
+        <f>_xlfn.XLOOKUP(C11, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F8E</v>
+      </c>
+      <c r="O11" t="str">
+        <f>IF(D11="", "", _xlfn.XLOOKUP(D11, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201214</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="0"/>
+        <v>0.68627450980392157</v>
+      </c>
+      <c r="Q11" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12">
+        <v>21</v>
+      </c>
+      <c r="D12">
+        <v>201213</v>
+      </c>
+      <c r="E12">
+        <v>21</v>
+      </c>
+      <c r="F12" s="2">
+        <v>59</v>
+      </c>
+      <c r="G12">
+        <v>69.599999999999994</v>
+      </c>
+      <c r="H12" s="2">
+        <v>47</v>
+      </c>
+      <c r="I12" s="2">
+        <v>36</v>
+      </c>
+      <c r="J12" s="3">
+        <v>42</v>
+      </c>
+      <c r="K12" t="s">
+        <v>132</v>
+      </c>
+      <c r="N12" t="str">
+        <f>_xlfn.XLOOKUP(C12, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F88</v>
+      </c>
+      <c r="O12" t="str">
+        <f>IF(D12="", "", _xlfn.XLOOKUP(D12, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201213</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="0"/>
+        <v>0.76595744680851063</v>
+      </c>
+      <c r="Q12" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13">
+        <v>23</v>
+      </c>
+      <c r="D13">
+        <v>201225</v>
+      </c>
+      <c r="E13">
+        <v>22</v>
+      </c>
+      <c r="F13" s="2">
+        <v>63.4</v>
+      </c>
+      <c r="G13">
+        <v>75.2</v>
+      </c>
+      <c r="H13" s="2">
+        <v>46</v>
+      </c>
+      <c r="I13" s="2">
+        <v>35</v>
+      </c>
+      <c r="J13" s="3">
+        <v>43</v>
+      </c>
+      <c r="K13" t="s">
+        <v>132</v>
+      </c>
+      <c r="N13" t="str">
+        <f>_xlfn.XLOOKUP(C13, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F85</v>
+      </c>
+      <c r="O13" t="str">
+        <f>IF(D13="", "", _xlfn.XLOOKUP(D13, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201225</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="0"/>
+        <v>0.76086956521739135</v>
+      </c>
+      <c r="Q13" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14">
+        <v>24</v>
+      </c>
+      <c r="D14">
+        <v>201224</v>
+      </c>
+      <c r="E14">
+        <v>23</v>
+      </c>
+      <c r="F14" s="2">
+        <v>65.400000000000006</v>
+      </c>
+      <c r="G14">
+        <v>77</v>
+      </c>
+      <c r="H14" s="2">
+        <v>51</v>
+      </c>
+      <c r="I14" s="2">
+        <v>57</v>
+      </c>
+      <c r="J14" s="3">
+        <v>45</v>
+      </c>
+      <c r="K14" t="s">
+        <v>132</v>
+      </c>
+      <c r="N14" t="str">
+        <f>_xlfn.XLOOKUP(C14, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F68</v>
+      </c>
+      <c r="O14" t="str">
+        <f>IF(D14="", "", _xlfn.XLOOKUP(D14, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v>A69-2801-201224</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="0"/>
+        <v>1.1176470588235294</v>
+      </c>
+      <c r="Q14" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15">
+        <v>25</v>
+      </c>
+      <c r="E15">
+        <v>24</v>
+      </c>
+      <c r="F15" s="2">
+        <v>61.4</v>
+      </c>
+      <c r="G15">
+        <v>72.3</v>
+      </c>
+      <c r="H15" s="2">
+        <v>47</v>
+      </c>
+      <c r="I15" s="2">
+        <v>36</v>
+      </c>
+      <c r="J15" s="3">
+        <v>43</v>
+      </c>
+      <c r="K15" t="s">
+        <v>132</v>
+      </c>
+      <c r="N15" t="str">
+        <f>_xlfn.XLOOKUP(C15, Sheet1!A:A, Sheet1!B:B, "")</f>
+        <v>3DD.003E185F69</v>
+      </c>
+      <c r="O15" t="str">
+        <f>IF(D15="", "", _xlfn.XLOOKUP(D15, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+      <c r="P15">
+        <f t="shared" si="0"/>
+        <v>0.76595744680851063</v>
+      </c>
+      <c r="Q15" t="str">
+        <f t="shared" si="1"/>
+        <v>SNS</v>
+      </c>
+      <c r="R15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="F16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="3"/>
+      <c r="O16" t="str">
+        <f>IF(D16="", "", _xlfn.XLOOKUP(D16, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="3"/>
+      <c r="O17" t="str">
+        <f>IF(D17="", "", _xlfn.XLOOKUP(D17, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="3"/>
+      <c r="O18" t="str">
+        <f>IF(D18="", "", _xlfn.XLOOKUP(D18, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
+      <c r="O19" t="str">
+        <f>IF(D19="", "", _xlfn.XLOOKUP(D19, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="3"/>
+      <c r="O20" t="str">
+        <f>IF(D20="", "", _xlfn.XLOOKUP(D20, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="3"/>
+      <c r="O21" t="str">
+        <f>IF(D21="", "", _xlfn.XLOOKUP(D21, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="3"/>
+      <c r="O22" t="str">
+        <f>IF(D22="", "", _xlfn.XLOOKUP(D22, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="3"/>
+      <c r="O23" t="str">
+        <f>IF(D23="", "", _xlfn.XLOOKUP(D23, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="3"/>
+      <c r="O24" t="str">
+        <f>IF(D24="", "", _xlfn.XLOOKUP(D24, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="3"/>
+      <c r="O25" t="str">
+        <f>IF(D25="", "", _xlfn.XLOOKUP(D25, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="3"/>
+      <c r="O26" t="str">
+        <f>IF(D26="", "", _xlfn.XLOOKUP(D26, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="3"/>
+      <c r="O27" t="str">
+        <f>IF(D27="", "", _xlfn.XLOOKUP(D27, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="3"/>
+      <c r="O28" t="str">
+        <f>IF(D28="", "", _xlfn.XLOOKUP(D28, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="3"/>
+      <c r="O29" t="str">
+        <f>IF(D29="", "", _xlfn.XLOOKUP(D29, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="3"/>
+      <c r="O30" t="str">
+        <f>IF(D30="", "", _xlfn.XLOOKUP(D30, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="3"/>
+      <c r="O31" t="str">
+        <f>IF(D31="", "", _xlfn.XLOOKUP(D31, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="3"/>
+      <c r="O32" t="str">
+        <f>IF(D32="", "", _xlfn.XLOOKUP(D32, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="3"/>
+      <c r="O33" t="str">
+        <f>IF(D33="", "", _xlfn.XLOOKUP(D33, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="3"/>
+      <c r="O34" t="str">
+        <f>IF(D34="", "", _xlfn.XLOOKUP(D34, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="3"/>
+      <c r="O35" t="str">
+        <f>IF(D35="", "", _xlfn.XLOOKUP(D35, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="3"/>
+      <c r="O36" t="str">
+        <f>IF(D36="", "", _xlfn.XLOOKUP(D36, Sheet1!F:F, Sheet1!E:E, ""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="3"/>
+    </row>
+    <row r="38" spans="6:15" x14ac:dyDescent="0.25">
+      <c r="F38" s="2"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{488E39B3-2C61-459C-8BA6-3DDB189E9E40}">
   <dimension ref="A1:Y36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.54296875" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" customWidth="1"/>
-    <col min="11" max="11" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7265625" customWidth="1"/>
-    <col min="17" max="17" width="12.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" customWidth="1"/>
+    <col min="17" max="17" width="12.140625" customWidth="1"/>
     <col min="18" max="18" width="4" customWidth="1"/>
-    <col min="20" max="20" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>88</v>
       </c>
@@ -7214,7 +7562,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25</v>
       </c>
@@ -7285,7 +7633,7 @@
         <v>4948116</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26</v>
       </c>
@@ -7336,7 +7684,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>27</v>
       </c>
@@ -7387,7 +7735,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>28</v>
       </c>
@@ -7438,7 +7786,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>29</v>
       </c>
@@ -7489,7 +7837,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>30</v>
       </c>
@@ -7540,7 +7888,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>31</v>
       </c>
@@ -7594,7 +7942,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>32</v>
       </c>
@@ -7647,7 +7995,7 @@
         <v>UKN</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>33</v>
       </c>
@@ -7700,7 +8048,7 @@
         <v>UKN</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>34</v>
       </c>
@@ -7753,7 +8101,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>35</v>
       </c>
@@ -7804,7 +8152,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>36</v>
       </c>
@@ -7855,7 +8203,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>37</v>
       </c>
@@ -7906,7 +8254,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>38</v>
       </c>
@@ -7960,7 +8308,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>39</v>
       </c>
@@ -8011,7 +8359,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="17" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N17" t="str">
         <f>IF(C17="", "", _xlfn.XLOOKUP(C17, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8021,7 +8369,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N18" t="str">
         <f>IF(C18="", "", _xlfn.XLOOKUP(C18, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8031,7 +8379,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N19" t="str">
         <f>IF(C19="", "", _xlfn.XLOOKUP(C19, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8041,7 +8389,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N20" t="str">
         <f>IF(C20="", "", _xlfn.XLOOKUP(C20, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8051,7 +8399,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N21" t="str">
         <f>IF(C21="", "", _xlfn.XLOOKUP(C21, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8061,7 +8409,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N22" t="str">
         <f>IF(C22="", "", _xlfn.XLOOKUP(C22, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8071,7 +8419,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N23" t="str">
         <f>IF(C23="", "", _xlfn.XLOOKUP(C23, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8081,7 +8429,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N24" t="str">
         <f>IF(C24="", "", _xlfn.XLOOKUP(C24, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8091,7 +8439,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N25" t="str">
         <f>IF(C25="", "", _xlfn.XLOOKUP(C25, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8101,7 +8449,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N26" t="str">
         <f>IF(C26="", "", _xlfn.XLOOKUP(C26, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8111,7 +8459,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N27" t="str">
         <f>IF(C27="", "", _xlfn.XLOOKUP(C27, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8121,7 +8469,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N28" t="str">
         <f>IF(C28="", "", _xlfn.XLOOKUP(C28, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8131,7 +8479,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N29" t="str">
         <f>IF(C29="", "", _xlfn.XLOOKUP(C29, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8141,7 +8489,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N30" t="str">
         <f>IF(C30="", "", _xlfn.XLOOKUP(C30, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8151,7 +8499,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N31" t="str">
         <f>IF(C31="", "", _xlfn.XLOOKUP(C31, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8161,7 +8509,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N32" t="str">
         <f>IF(C32="", "", _xlfn.XLOOKUP(C32, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8171,7 +8519,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N33" t="str">
         <f>IF(C33="", "", _xlfn.XLOOKUP(C33, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8181,7 +8529,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N34" t="str">
         <f>IF(C34="", "", _xlfn.XLOOKUP(C34, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8191,13 +8539,13 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N35" t="str">
         <f>IF(C35="", "", _xlfn.XLOOKUP(C35, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="14:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="14:15" x14ac:dyDescent="0.25">
       <c r="N36" t="str">
         <f>IF(C36="", "", _xlfn.XLOOKUP(C36, Sheet1!A:A, Sheet1!B:B, ""))</f>
         <v/>
@@ -8205,13 +8553,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="Q2:Q36">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>$Q2="UKN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="2" stopIfTrue="1">
       <formula>AND($Q2=$B2, $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="3" stopIfTrue="1">
       <formula>AND($Q2&lt;&gt;$B2, $Q2&lt;&gt;"UKN", $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8219,32 +8567,32 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06DEAEC3-E597-43CF-8A39-542D98AFB6F7}">
   <dimension ref="A1:Y38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.54296875" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" customWidth="1"/>
-    <col min="11" max="11" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7265625" customWidth="1"/>
-    <col min="17" max="17" width="12.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" customWidth="1"/>
+    <col min="17" max="17" width="12.140625" customWidth="1"/>
     <col min="18" max="18" width="4" customWidth="1"/>
-    <col min="20" max="20" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>88</v>
       </c>
@@ -8315,7 +8663,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>40</v>
       </c>
@@ -8384,7 +8732,7 @@
         <v>4948116</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>41</v>
       </c>
@@ -8435,7 +8783,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>42</v>
       </c>
@@ -8486,7 +8834,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>43</v>
       </c>
@@ -8534,7 +8882,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>44</v>
       </c>
@@ -8582,7 +8930,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>45</v>
       </c>
@@ -8633,7 +8981,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>46</v>
       </c>
@@ -8681,7 +9029,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>47</v>
       </c>
@@ -8729,7 +9077,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>48</v>
       </c>
@@ -8780,7 +9128,7 @@
         <v>AST</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>49</v>
       </c>
@@ -8831,7 +9179,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>50</v>
       </c>
@@ -8882,7 +9230,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>51</v>
       </c>
@@ -8935,7 +9283,7 @@
         <v>SNS</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -8949,7 +9297,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -8963,7 +9311,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -8977,7 +9325,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -8991,7 +9339,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -9005,7 +9353,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -9019,7 +9367,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -9033,7 +9381,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -9047,7 +9395,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -9061,7 +9409,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -9075,7 +9423,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -9089,7 +9437,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -9103,7 +9451,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -9117,7 +9465,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -9131,7 +9479,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -9145,7 +9493,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -9159,7 +9507,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -9173,7 +9521,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -9187,7 +9535,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -9201,7 +9549,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -9215,7 +9563,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -9229,7 +9577,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -9239,7 +9587,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -9249,25 +9597,25 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F38" s="2"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <conditionalFormatting sqref="Q2:Q100">
-    <cfRule type="expression" dxfId="6" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="1" stopIfTrue="1">
       <formula>AND($Q2&lt;&gt;$B2, $Q2&lt;&gt;"UKN", $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>$Q2="UKN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="3" stopIfTrue="1">
       <formula>AND($Q2=$B2, $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9275,32 +9623,32 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7092AF79-999B-48C9-8AAD-B4913AEC6A18}">
   <dimension ref="A1:Y38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.54296875" customWidth="1"/>
-    <col min="10" max="10" width="7.7265625" customWidth="1"/>
-    <col min="11" max="11" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7265625" customWidth="1"/>
-    <col min="17" max="17" width="12.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" customWidth="1"/>
+    <col min="17" max="17" width="12.140625" customWidth="1"/>
     <col min="18" max="18" width="4" customWidth="1"/>
-    <col min="20" max="20" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:25" s="13" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>88</v>
       </c>
@@ -9371,7 +9719,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>52</v>
       </c>
@@ -9443,7 +9791,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>53</v>
       </c>
@@ -9499,7 +9847,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>54</v>
       </c>
@@ -9553,7 +9901,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>55</v>
       </c>
@@ -9607,7 +9955,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>56</v>
       </c>
@@ -9661,7 +10009,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>57</v>
       </c>
@@ -9712,7 +10060,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>58</v>
       </c>
@@ -9763,7 +10111,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>59</v>
       </c>
@@ -9814,7 +10162,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>60</v>
       </c>
@@ -9865,7 +10213,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>61</v>
       </c>
@@ -9916,7 +10264,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>62</v>
       </c>
@@ -9967,7 +10315,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>63</v>
       </c>
@@ -10020,7 +10368,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -10034,7 +10382,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -10048,7 +10396,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="F16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -10062,7 +10410,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -10076,7 +10424,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -10090,7 +10438,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -10104,7 +10452,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -10118,7 +10466,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -10132,7 +10480,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -10146,7 +10494,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -10160,7 +10508,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -10174,7 +10522,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -10188,7 +10536,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -10202,7 +10550,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -10216,7 +10564,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -10230,7 +10578,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -10244,7 +10592,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -10258,7 +10606,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -10272,7 +10620,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -10286,7 +10634,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -10300,7 +10648,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -10314,7 +10662,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -10324,7 +10672,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -10334,25 +10682,25 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="6:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="6:15" x14ac:dyDescent="0.25">
       <c r="F38" s="2"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <conditionalFormatting sqref="Q2:Q100">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
       <formula>AND($Q2&lt;&gt;$B2, $Q2&lt;&gt;"UKN", $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>$Q2="UKN"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
       <formula>AND($Q2=$B2, $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/tagsheet_to_tidbits2025/data/Sander's PIT CODES.xlsx
+++ b/tagsheet_to_tidbits2025/data/Sander's PIT CODES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://umainesystem-my.sharepoint.com/personal/sander_elliott_maine_edu/Documents/Desktop/Github/Sturgeon_TidBits/tagsheet_to_tidbits2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{87E30D02-C812-421C-A0AA-2F4032EB8D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D613798-27E4-42F6-8F60-023531AB6DF7}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{87E30D02-C812-421C-A0AA-2F4032EB8D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAA3E067-F1CF-4C23-BA8A-A0A1D0F9DE7B}"/>
   <bookViews>
-    <workbookView xWindow="29070" yWindow="0" windowWidth="28530" windowHeight="15480" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28755" yWindow="285" windowWidth="28530" windowHeight="15480" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trip" sheetId="7" r:id="rId1"/>
@@ -1148,7 +1148,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
@@ -1176,7 +1176,6 @@
     <xf numFmtId="0" fontId="17" fillId="13" borderId="11" xfId="22" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1339,6 +1338,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3356,7 +3359,7 @@
         <f>VALUE(RIGHT(E2,6))</f>
         <v>201133</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2">
         <v>1645258</v>
       </c>
       <c r="I2" t="s">
@@ -3380,7 +3383,7 @@
         <f t="shared" ref="F3:F51" si="0">VALUE(RIGHT(E3,6))</f>
         <v>201127</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3">
         <v>1645259</v>
       </c>
       <c r="I3" t="s">
@@ -3413,7 +3416,7 @@
         <f t="shared" si="0"/>
         <v>201134</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4">
         <v>1645260</v>
       </c>
       <c r="I4" t="s">
@@ -3449,7 +3452,7 @@
         <f t="shared" si="0"/>
         <v>201128</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5">
         <v>1645261</v>
       </c>
       <c r="I5" t="s">
@@ -3485,7 +3488,7 @@
         <f t="shared" si="0"/>
         <v>201129</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6">
         <v>1645262</v>
       </c>
       <c r="I6" t="s">
@@ -3521,7 +3524,7 @@
         <f t="shared" si="0"/>
         <v>201131</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7">
         <v>1645263</v>
       </c>
       <c r="I7" t="s">
@@ -3557,7 +3560,7 @@
         <f t="shared" si="0"/>
         <v>201130</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8">
         <v>1645264</v>
       </c>
       <c r="I8" t="s">
@@ -3593,7 +3596,7 @@
         <f t="shared" si="0"/>
         <v>201132</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9">
         <v>1645265</v>
       </c>
       <c r="I9" t="s">
@@ -3629,7 +3632,7 @@
         <f t="shared" si="0"/>
         <v>201212</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10">
         <v>1645266</v>
       </c>
       <c r="I10" t="s">
@@ -3665,7 +3668,7 @@
         <f t="shared" si="0"/>
         <v>201215</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11">
         <v>1645267</v>
       </c>
       <c r="I11" t="s">
@@ -3701,7 +3704,7 @@
         <f t="shared" si="0"/>
         <v>201213</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12">
         <v>1645268</v>
       </c>
       <c r="I12" t="s">
@@ -3737,7 +3740,7 @@
         <f t="shared" si="0"/>
         <v>201214</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13">
         <v>1645269</v>
       </c>
       <c r="I13" t="s">
@@ -3773,7 +3776,7 @@
         <f t="shared" si="0"/>
         <v>201216</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14">
         <v>1645270</v>
       </c>
       <c r="I14" t="s">
@@ -3809,7 +3812,7 @@
         <f t="shared" si="0"/>
         <v>201217</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15">
         <v>1645271</v>
       </c>
       <c r="I15" t="s">
@@ -3845,7 +3848,7 @@
         <f t="shared" si="0"/>
         <v>201218</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16">
         <v>1645272</v>
       </c>
       <c r="I16" t="s">
@@ -3881,7 +3884,7 @@
         <f t="shared" si="0"/>
         <v>201219</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17">
         <v>1645273</v>
       </c>
       <c r="I17" t="s">
@@ -3917,7 +3920,7 @@
         <f t="shared" si="0"/>
         <v>201220</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18">
         <v>1645274</v>
       </c>
       <c r="I18" t="s">
@@ -3953,7 +3956,7 @@
         <f t="shared" si="0"/>
         <v>201223</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19">
         <v>1645275</v>
       </c>
       <c r="I19" t="s">
@@ -3989,7 +3992,7 @@
         <f t="shared" si="0"/>
         <v>201222</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20">
         <v>1645276</v>
       </c>
       <c r="I20" t="s">
@@ -4025,7 +4028,7 @@
         <f t="shared" si="0"/>
         <v>201221</v>
       </c>
-      <c r="H21" s="15">
+      <c r="H21">
         <v>1645277</v>
       </c>
       <c r="I21" t="s">
@@ -4061,7 +4064,7 @@
         <f t="shared" si="0"/>
         <v>201224</v>
       </c>
-      <c r="H22" s="15">
+      <c r="H22">
         <v>1645278</v>
       </c>
       <c r="I22" t="s">
@@ -4097,7 +4100,7 @@
         <f t="shared" si="0"/>
         <v>201225</v>
       </c>
-      <c r="H23" s="15">
+      <c r="H23">
         <v>1645279</v>
       </c>
       <c r="I23" t="s">
@@ -4133,7 +4136,7 @@
         <f t="shared" si="0"/>
         <v>201226</v>
       </c>
-      <c r="H24" s="15">
+      <c r="H24">
         <v>1645280</v>
       </c>
       <c r="I24" t="s">
@@ -4169,7 +4172,7 @@
         <f t="shared" si="0"/>
         <v>201227</v>
       </c>
-      <c r="H25" s="15">
+      <c r="H25">
         <v>1645281</v>
       </c>
       <c r="I25" t="s">
@@ -4205,7 +4208,7 @@
         <f t="shared" si="0"/>
         <v>201228</v>
       </c>
-      <c r="H26" s="15">
+      <c r="H26">
         <v>1645282</v>
       </c>
       <c r="I26" t="s">
@@ -4241,7 +4244,7 @@
         <f t="shared" si="0"/>
         <v>201229</v>
       </c>
-      <c r="H27" s="15">
+      <c r="H27">
         <v>1645283</v>
       </c>
       <c r="I27" t="s">
@@ -4277,7 +4280,7 @@
         <f t="shared" si="0"/>
         <v>201232</v>
       </c>
-      <c r="H28" s="15">
+      <c r="H28">
         <v>1645284</v>
       </c>
       <c r="I28" t="s">
@@ -4313,7 +4316,7 @@
         <f t="shared" si="0"/>
         <v>201231</v>
       </c>
-      <c r="H29" s="15">
+      <c r="H29">
         <v>1645285</v>
       </c>
       <c r="I29" t="s">
@@ -4349,7 +4352,7 @@
         <f t="shared" si="0"/>
         <v>201230</v>
       </c>
-      <c r="H30" s="15">
+      <c r="H30">
         <v>1645286</v>
       </c>
       <c r="I30" t="s">
@@ -4385,7 +4388,7 @@
         <f t="shared" si="0"/>
         <v>201235</v>
       </c>
-      <c r="H31" s="15">
+      <c r="H31">
         <v>1645287</v>
       </c>
       <c r="I31" t="s">
@@ -4421,7 +4424,7 @@
         <f t="shared" si="0"/>
         <v>201234</v>
       </c>
-      <c r="H32" s="15">
+      <c r="H32">
         <v>1645288</v>
       </c>
       <c r="I32" t="s">
@@ -4457,7 +4460,7 @@
         <f t="shared" si="0"/>
         <v>201233</v>
       </c>
-      <c r="H33" s="15">
+      <c r="H33">
         <v>1645289</v>
       </c>
       <c r="I33" t="s">
@@ -4493,7 +4496,7 @@
         <f t="shared" si="0"/>
         <v>201238</v>
       </c>
-      <c r="H34" s="15">
+      <c r="H34">
         <v>1645290</v>
       </c>
       <c r="I34" t="s">
@@ -4529,7 +4532,7 @@
         <f t="shared" si="0"/>
         <v>201237</v>
       </c>
-      <c r="H35" s="15">
+      <c r="H35">
         <v>1645291</v>
       </c>
       <c r="I35" t="s">
@@ -4565,7 +4568,7 @@
         <f t="shared" si="0"/>
         <v>201236</v>
       </c>
-      <c r="H36" s="15">
+      <c r="H36">
         <v>1645292</v>
       </c>
       <c r="I36" t="s">
@@ -4601,7 +4604,7 @@
         <f t="shared" si="0"/>
         <v>201239</v>
       </c>
-      <c r="H37" s="15">
+      <c r="H37">
         <v>1645293</v>
       </c>
       <c r="I37" t="s">
@@ -4637,7 +4640,7 @@
         <f t="shared" si="0"/>
         <v>201240</v>
       </c>
-      <c r="H38" s="15">
+      <c r="H38">
         <v>1645294</v>
       </c>
       <c r="I38" t="s">
@@ -4673,7 +4676,7 @@
         <f t="shared" si="0"/>
         <v>201241</v>
       </c>
-      <c r="H39" s="15">
+      <c r="H39">
         <v>1645295</v>
       </c>
       <c r="I39" t="s">
@@ -4709,7 +4712,7 @@
         <f t="shared" si="0"/>
         <v>201244</v>
       </c>
-      <c r="H40" s="15">
+      <c r="H40">
         <v>1645296</v>
       </c>
       <c r="I40" t="s">
@@ -4745,7 +4748,7 @@
         <f t="shared" si="0"/>
         <v>201243</v>
       </c>
-      <c r="H41" s="15">
+      <c r="H41">
         <v>1645297</v>
       </c>
       <c r="I41" t="s">
@@ -4781,7 +4784,7 @@
         <f t="shared" si="0"/>
         <v>201242</v>
       </c>
-      <c r="H42" s="15">
+      <c r="H42">
         <v>1645298</v>
       </c>
       <c r="I42" t="s">
@@ -4817,7 +4820,7 @@
         <f t="shared" si="0"/>
         <v>201247</v>
       </c>
-      <c r="H43" s="15">
+      <c r="H43">
         <v>1645299</v>
       </c>
       <c r="I43" t="s">
@@ -5141,7 +5144,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2">
         <v>1645258</v>
       </c>
       <c r="B2" t="s">
@@ -5149,7 +5152,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3">
         <v>1645259</v>
       </c>
       <c r="B3" t="s">
@@ -5157,7 +5160,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
+      <c r="A4">
         <v>1645260</v>
       </c>
       <c r="B4" t="s">
@@ -5165,7 +5168,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5">
         <v>1645261</v>
       </c>
       <c r="B5" t="s">
@@ -5173,7 +5176,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6">
         <v>1645262</v>
       </c>
       <c r="B6" t="s">
@@ -5181,7 +5184,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
+      <c r="A7">
         <v>1645263</v>
       </c>
       <c r="B7" t="s">
@@ -5189,7 +5192,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
+      <c r="A8">
         <v>1645264</v>
       </c>
       <c r="B8" t="s">
@@ -5197,7 +5200,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9">
         <v>1645265</v>
       </c>
       <c r="B9" t="s">
@@ -5205,7 +5208,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10">
         <v>1645266</v>
       </c>
       <c r="B10" t="s">
@@ -5213,7 +5216,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="A11">
         <v>1645267</v>
       </c>
       <c r="B11" t="s">
@@ -5221,7 +5224,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="15">
+      <c r="A12">
         <v>1645268</v>
       </c>
       <c r="B12" t="s">
@@ -5229,7 +5232,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
+      <c r="A13">
         <v>1645269</v>
       </c>
       <c r="B13" t="s">
@@ -5237,7 +5240,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
+      <c r="A14">
         <v>1645270</v>
       </c>
       <c r="B14" t="s">
@@ -5245,7 +5248,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
+      <c r="A15">
         <v>1645271</v>
       </c>
       <c r="B15" t="s">
@@ -5253,7 +5256,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="15">
+      <c r="A16">
         <v>1645272</v>
       </c>
       <c r="B16" t="s">
@@ -5261,7 +5264,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="15">
+      <c r="A17">
         <v>1645273</v>
       </c>
       <c r="B17" t="s">
@@ -5269,7 +5272,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
+      <c r="A18">
         <v>1645274</v>
       </c>
       <c r="B18" t="s">
@@ -5277,7 +5280,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="15">
+      <c r="A19">
         <v>1645275</v>
       </c>
       <c r="B19" t="s">
@@ -5285,7 +5288,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="15">
+      <c r="A20">
         <v>1645276</v>
       </c>
       <c r="B20" t="s">
@@ -5293,7 +5296,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="15">
+      <c r="A21">
         <v>1645277</v>
       </c>
       <c r="B21" t="s">
@@ -5301,7 +5304,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
+      <c r="A22">
         <v>1645278</v>
       </c>
       <c r="B22" t="s">
@@ -5309,7 +5312,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="15">
+      <c r="A23">
         <v>1645279</v>
       </c>
       <c r="B23" t="s">
@@ -5317,7 +5320,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
+      <c r="A24">
         <v>1645280</v>
       </c>
       <c r="B24" t="s">
@@ -5325,7 +5328,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="15">
+      <c r="A25">
         <v>1645281</v>
       </c>
       <c r="B25" t="s">
@@ -5333,7 +5336,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
+      <c r="A26">
         <v>1645282</v>
       </c>
       <c r="B26" t="s">
@@ -5341,7 +5344,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="15">
+      <c r="A27">
         <v>1645283</v>
       </c>
       <c r="B27" t="s">
@@ -5349,7 +5352,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="15">
+      <c r="A28">
         <v>1645284</v>
       </c>
       <c r="B28" t="s">
@@ -5357,7 +5360,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="15">
+      <c r="A29">
         <v>1645285</v>
       </c>
       <c r="B29" t="s">
@@ -5365,7 +5368,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="15">
+      <c r="A30">
         <v>1645286</v>
       </c>
       <c r="B30" t="s">
@@ -5373,7 +5376,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="15">
+      <c r="A31">
         <v>1645287</v>
       </c>
       <c r="B31" t="s">
@@ -5381,7 +5384,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="15">
+      <c r="A32">
         <v>1645288</v>
       </c>
       <c r="B32" t="s">
@@ -5389,7 +5392,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="15">
+      <c r="A33">
         <v>1645289</v>
       </c>
       <c r="B33" t="s">
@@ -5397,7 +5400,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="15">
+      <c r="A34">
         <v>1645290</v>
       </c>
       <c r="B34" t="s">
@@ -5405,7 +5408,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="15">
+      <c r="A35">
         <v>1645291</v>
       </c>
       <c r="B35" t="s">
@@ -5413,7 +5416,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="15">
+      <c r="A36">
         <v>1645292</v>
       </c>
       <c r="B36" t="s">
@@ -5421,7 +5424,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="15">
+      <c r="A37">
         <v>1645293</v>
       </c>
       <c r="B37" t="s">
@@ -5429,7 +5432,7 @@
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="15">
+      <c r="A38">
         <v>1645294</v>
       </c>
       <c r="B38" t="s">
@@ -5437,7 +5440,7 @@
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="15">
+      <c r="A39">
         <v>1645295</v>
       </c>
       <c r="B39" t="s">
@@ -5445,7 +5448,7 @@
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="15">
+      <c r="A40">
         <v>1645296</v>
       </c>
       <c r="B40" t="s">
@@ -5453,7 +5456,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="15">
+      <c r="A41">
         <v>1645297</v>
       </c>
       <c r="B41" t="s">
@@ -5461,7 +5464,7 @@
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="15">
+      <c r="A42">
         <v>1645298</v>
       </c>
       <c r="B42" t="s">
@@ -5469,7 +5472,7 @@
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="15">
+      <c r="A43">
         <v>1645299</v>
       </c>
       <c r="B43" t="s">
@@ -9187,7 +9190,7 @@
         <v>140</v>
       </c>
       <c r="C12">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12">
         <v>201251</v>
@@ -9215,7 +9218,7 @@
       </c>
       <c r="N12" t="str">
         <f>IF(C12="", "", _xlfn.XLOOKUP(C12, Sheet1!A:A, Sheet1!B:B, ""))</f>
-        <v>3DD.003E185F84</v>
+        <v>3DD.003E185F67</v>
       </c>
       <c r="O12" t="str">
         <f>IF(D12="", "", _xlfn.XLOOKUP(D12, Sheet1!F:F, Sheet1!E:E, ""))</f>
@@ -9607,7 +9610,6 @@
       <c r="F38" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <conditionalFormatting sqref="Q2:Q100">
     <cfRule type="expression" dxfId="5" priority="1" stopIfTrue="1">
       <formula>AND($Q2&lt;&gt;$B2, $Q2&lt;&gt;"UKN", $Q2&lt;&gt;"", $B2&lt;&gt;"")</formula>
